--- a/research/traditional_assets/database/data/cyprus/cyprus_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_metals_mining.xlsx
@@ -1377,13 +1377,13 @@
         <v>632.6</v>
       </c>
       <c r="L2">
-        <v>586.334123107818</v>
+        <v>586.334123107817</v>
       </c>
       <c r="M2">
         <v>591.7</v>
       </c>
       <c r="N2">
-        <v>602.754123107818</v>
+        <v>602.754123107817</v>
       </c>
       <c r="O2">
         <v>44.2</v>
@@ -1504,7 +1504,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1641,22 +1641,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1041710588458377</v>
+        <v>0.1040802200222804</v>
       </c>
       <c r="C2">
-        <v>680.5603589258744</v>
+        <v>674.7204768784003</v>
       </c>
       <c r="D2">
-        <v>595.4603589258744</v>
+        <v>596.3884768784003</v>
       </c>
       <c r="E2">
-        <v>-44.2</v>
+        <v>-37.432</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.768000000000001</v>
       </c>
       <c r="G2">
         <v>85.09999999999999</v>
@@ -1677,28 +1677,28 @@
         <v>26.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3404304</v>
       </c>
       <c r="N2">
-        <v>26.6</v>
+        <v>26.2595696</v>
       </c>
       <c r="O2">
-        <v>3.325</v>
+        <v>3.2824462</v>
       </c>
       <c r="P2">
-        <v>23.275</v>
+        <v>22.9771234</v>
       </c>
       <c r="Q2">
-        <v>71.875</v>
+        <v>71.5771234</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1041710588458377</v>
+        <v>0.1046869646689701</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9929188226047619</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>78.13638264972811</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1723,22 +1723,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1040802200222804</v>
+        <v>0.1039893811987231</v>
       </c>
       <c r="C3">
-        <v>674.7204768784003</v>
+        <v>668.8834925810374</v>
       </c>
       <c r="D3">
-        <v>596.3884768784003</v>
+        <v>597.3194925810375</v>
       </c>
       <c r="E3">
-        <v>-37.432</v>
+        <v>-30.664</v>
       </c>
       <c r="F3">
-        <v>6.768000000000001</v>
+        <v>13.536</v>
       </c>
       <c r="G3">
         <v>85.09999999999999</v>
@@ -1759,28 +1759,28 @@
         <v>26.6</v>
       </c>
       <c r="M3">
-        <v>0.3404304</v>
+        <v>0.6808608</v>
       </c>
       <c r="N3">
-        <v>26.2595696</v>
+        <v>25.9191392</v>
       </c>
       <c r="O3">
-        <v>3.2824462</v>
+        <v>3.2398924</v>
       </c>
       <c r="P3">
-        <v>22.9771234</v>
+        <v>22.6792468</v>
       </c>
       <c r="Q3">
-        <v>71.5771234</v>
+        <v>71.27924680000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1046869646689701</v>
+        <v>0.1052133991823705</v>
       </c>
       <c r="T3">
-        <v>0.9929188226047619</v>
+        <v>1.00179526478789</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>78.13638264972811</v>
+        <v>39.06819132486405</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1805,22 +1805,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1039893811987231</v>
+        <v>0.1038985423751658</v>
       </c>
       <c r="C4">
-        <v>668.8834925810374</v>
+        <v>663.0494196259457</v>
       </c>
       <c r="D4">
-        <v>597.3194925810375</v>
+        <v>598.2534196259456</v>
       </c>
       <c r="E4">
-        <v>-30.664</v>
+        <v>-23.896</v>
       </c>
       <c r="F4">
-        <v>13.536</v>
+        <v>20.304</v>
       </c>
       <c r="G4">
         <v>85.09999999999999</v>
@@ -1841,28 +1841,28 @@
         <v>26.6</v>
       </c>
       <c r="M4">
-        <v>0.6808608</v>
+        <v>1.0212912</v>
       </c>
       <c r="N4">
-        <v>25.9191392</v>
+        <v>25.5787088</v>
       </c>
       <c r="O4">
-        <v>3.2398924</v>
+        <v>3.1973386</v>
       </c>
       <c r="P4">
-        <v>22.6792468</v>
+        <v>22.3813702</v>
       </c>
       <c r="Q4">
-        <v>71.27924680000001</v>
+        <v>70.9813702</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1052133991823705</v>
+        <v>0.1057506880156349</v>
       </c>
       <c r="T4">
-        <v>1.00179526478789</v>
+        <v>1.010854726397475</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.06819132486405</v>
+        <v>26.0454608832427</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1887,22 +1887,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1038985423751658</v>
+        <v>0.1038077035516085</v>
       </c>
       <c r="C5">
-        <v>663.0494196259457</v>
+        <v>657.2182716904238</v>
       </c>
       <c r="D5">
-        <v>598.2534196259456</v>
+        <v>599.1902716904237</v>
       </c>
       <c r="E5">
-        <v>-23.896</v>
+        <v>-17.128</v>
       </c>
       <c r="F5">
-        <v>20.304</v>
+        <v>27.072</v>
       </c>
       <c r="G5">
         <v>85.09999999999999</v>
@@ -1923,28 +1923,28 @@
         <v>26.6</v>
       </c>
       <c r="M5">
-        <v>1.0212912</v>
+        <v>1.3617216</v>
       </c>
       <c r="N5">
-        <v>25.5787088</v>
+        <v>25.2382784</v>
       </c>
       <c r="O5">
-        <v>3.1973386</v>
+        <v>3.1547848</v>
       </c>
       <c r="P5">
-        <v>22.3813702</v>
+        <v>22.0834936</v>
       </c>
       <c r="Q5">
-        <v>70.9813702</v>
+        <v>70.68349360000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1057506880156349</v>
+        <v>0.1062991703662589</v>
       </c>
       <c r="T5">
-        <v>1.010854726397475</v>
+        <v>1.020102926790593</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.0454608832427</v>
+        <v>19.53409566243203</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1969,22 +1969,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1038077035516085</v>
+        <v>0.1037168647280512</v>
       </c>
       <c r="C6">
-        <v>657.2182716904238</v>
+        <v>651.3900625375787</v>
       </c>
       <c r="D6">
-        <v>599.1902716904237</v>
+        <v>600.1300625375787</v>
       </c>
       <c r="E6">
-        <v>-17.128</v>
+        <v>-10.36</v>
       </c>
       <c r="F6">
-        <v>27.072</v>
+        <v>33.84</v>
       </c>
       <c r="G6">
         <v>85.09999999999999</v>
@@ -2005,28 +2005,28 @@
         <v>26.6</v>
       </c>
       <c r="M6">
-        <v>1.3617216</v>
+        <v>1.702152</v>
       </c>
       <c r="N6">
-        <v>25.2382784</v>
+        <v>24.897848</v>
       </c>
       <c r="O6">
-        <v>3.1547848</v>
+        <v>3.112231</v>
       </c>
       <c r="P6">
-        <v>22.0834936</v>
+        <v>21.785617</v>
       </c>
       <c r="Q6">
-        <v>70.68349360000001</v>
+        <v>70.385617</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1062991703662589</v>
+        <v>0.1068591997137382</v>
       </c>
       <c r="T6">
-        <v>1.020102926790593</v>
+        <v>1.029545826139356</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.53409566243203</v>
+        <v>15.62727652994562</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2051,22 +2051,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1037168647280512</v>
+        <v>0.1036260259044939</v>
       </c>
       <c r="C7">
-        <v>651.3900625375787</v>
+        <v>645.5648060169995</v>
       </c>
       <c r="D7">
-        <v>600.1300625375787</v>
+        <v>601.0728060169994</v>
       </c>
       <c r="E7">
-        <v>-10.36</v>
+        <v>-3.591999999999999</v>
       </c>
       <c r="F7">
-        <v>33.84</v>
+        <v>40.608</v>
       </c>
       <c r="G7">
         <v>85.09999999999999</v>
@@ -2087,28 +2087,28 @@
         <v>26.6</v>
       </c>
       <c r="M7">
-        <v>1.702152</v>
+        <v>2.0425824</v>
       </c>
       <c r="N7">
-        <v>24.897848</v>
+        <v>24.5574176</v>
       </c>
       <c r="O7">
-        <v>3.112231</v>
+        <v>3.0696772</v>
       </c>
       <c r="P7">
-        <v>21.785617</v>
+        <v>21.4877404</v>
       </c>
       <c r="Q7">
-        <v>70.385617</v>
+        <v>70.0877404</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1068591997137382</v>
+        <v>0.1074311445792489</v>
       </c>
       <c r="T7">
-        <v>1.029545826139356</v>
+        <v>1.039189638240219</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.62727652994562</v>
+        <v>13.02273044162135</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1036260259044939</v>
+        <v>0.1036270620809367</v>
       </c>
       <c r="C8">
-        <v>645.5648060169995</v>
+        <v>638.786035670737</v>
       </c>
       <c r="D8">
-        <v>601.0728060169994</v>
+        <v>601.0620356707369</v>
       </c>
       <c r="E8">
-        <v>-3.591999999999999</v>
+        <v>3.175999999999995</v>
       </c>
       <c r="F8">
-        <v>40.608</v>
+        <v>47.376</v>
       </c>
       <c r="G8">
         <v>85.09999999999999</v>
@@ -2169,45 +2169,45 @@
         <v>26.6</v>
       </c>
       <c r="M8">
-        <v>2.0425824</v>
+        <v>2.4540768</v>
       </c>
       <c r="N8">
-        <v>24.5574176</v>
+        <v>24.1459232</v>
       </c>
       <c r="O8">
-        <v>3.0696772</v>
+        <v>3.0182404</v>
       </c>
       <c r="P8">
-        <v>21.4877404</v>
+        <v>21.1276828</v>
       </c>
       <c r="Q8">
-        <v>70.0877404</v>
+        <v>69.7276828</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1074311445792489</v>
+        <v>0.1080153893343405</v>
       </c>
       <c r="T8">
-        <v>1.039189638240219</v>
+        <v>1.049040844149704</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.02273044162135</v>
+        <v>10.83910658378744</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2215,22 +2215,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1036270620809367</v>
+        <v>0.1036683482573794</v>
       </c>
       <c r="C9">
-        <v>638.7860356707371</v>
+        <v>631.5892079262965</v>
       </c>
       <c r="D9">
-        <v>601.062035670737</v>
+        <v>600.6332079262964</v>
       </c>
       <c r="E9">
-        <v>3.176000000000009</v>
+        <v>9.944000000000003</v>
       </c>
       <c r="F9">
-        <v>47.37600000000001</v>
+        <v>54.14400000000001</v>
       </c>
       <c r="G9">
         <v>85.09999999999999</v>
@@ -2251,45 +2251,45 @@
         <v>26.6</v>
       </c>
       <c r="M9">
-        <v>2.454076800000001</v>
+        <v>2.896704</v>
       </c>
       <c r="N9">
-        <v>24.1459232</v>
+        <v>23.703296</v>
       </c>
       <c r="O9">
-        <v>3.0182404</v>
+        <v>2.962912</v>
       </c>
       <c r="P9">
-        <v>21.1276828</v>
+        <v>20.740384</v>
       </c>
       <c r="Q9">
-        <v>69.7276828</v>
+        <v>69.340384</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1080153893343405</v>
+        <v>0.1086123350623689</v>
       </c>
       <c r="T9">
-        <v>1.049040844149704</v>
+        <v>1.059106206709395</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.83910658378743</v>
+        <v>9.182850577760103</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2297,22 +2297,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1036683482573794</v>
+        <v>0.1036055094338221</v>
       </c>
       <c r="C10">
-        <v>631.5892079262965</v>
+        <v>625.474140225401</v>
       </c>
       <c r="D10">
-        <v>600.6332079262964</v>
+        <v>601.286140225401</v>
       </c>
       <c r="E10">
-        <v>9.944000000000003</v>
+        <v>16.712</v>
       </c>
       <c r="F10">
-        <v>54.14400000000001</v>
+        <v>60.91200000000001</v>
       </c>
       <c r="G10">
         <v>85.09999999999999</v>
@@ -2333,28 +2333,28 @@
         <v>26.6</v>
       </c>
       <c r="M10">
-        <v>2.896704</v>
+        <v>3.258792</v>
       </c>
       <c r="N10">
-        <v>23.703296</v>
+        <v>23.341208</v>
       </c>
       <c r="O10">
-        <v>2.962912</v>
+        <v>2.917651</v>
       </c>
       <c r="P10">
-        <v>20.740384</v>
+        <v>20.423557</v>
       </c>
       <c r="Q10">
-        <v>69.340384</v>
+        <v>69.02355700000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1086123350623689</v>
+        <v>0.1092224004767275</v>
       </c>
       <c r="T10">
-        <v>1.059106206709395</v>
+        <v>1.069392786028639</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.182850577760103</v>
+        <v>8.162533846897869</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2379,22 +2379,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1036055094338221</v>
+        <v>0.1036126706102648</v>
       </c>
       <c r="C11">
-        <v>625.474140225401</v>
+        <v>618.6316597335424</v>
       </c>
       <c r="D11">
-        <v>601.286140225401</v>
+        <v>601.2116597335424</v>
       </c>
       <c r="E11">
-        <v>16.712</v>
+        <v>23.48</v>
       </c>
       <c r="F11">
-        <v>60.91200000000001</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="G11">
         <v>85.09999999999999</v>
@@ -2415,45 +2415,45 @@
         <v>26.6</v>
       </c>
       <c r="M11">
-        <v>3.258792</v>
+        <v>3.675024000000001</v>
       </c>
       <c r="N11">
-        <v>23.341208</v>
+        <v>22.924976</v>
       </c>
       <c r="O11">
-        <v>2.917651</v>
+        <v>2.865622</v>
       </c>
       <c r="P11">
-        <v>20.423557</v>
+        <v>20.059354</v>
       </c>
       <c r="Q11">
-        <v>69.02355700000001</v>
+        <v>68.65935400000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1092224004767275</v>
+        <v>0.1098460229002942</v>
       </c>
       <c r="T11">
-        <v>1.069392786028639</v>
+        <v>1.079907955999422</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.162533846897869</v>
+        <v>7.23804796921054</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2461,22 +2461,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1036126706102648</v>
+        <v>0.1035568317867075</v>
       </c>
       <c r="C12">
-        <v>618.6316597335424</v>
+        <v>612.4449061549603</v>
       </c>
       <c r="D12">
-        <v>601.2116597335424</v>
+        <v>601.7929061549603</v>
       </c>
       <c r="E12">
-        <v>23.48</v>
+        <v>30.248</v>
       </c>
       <c r="F12">
-        <v>67.68000000000001</v>
+        <v>74.44800000000001</v>
       </c>
       <c r="G12">
         <v>85.09999999999999</v>
@@ -2497,28 +2497,28 @@
         <v>26.6</v>
       </c>
       <c r="M12">
-        <v>3.675024000000001</v>
+        <v>4.042526400000001</v>
       </c>
       <c r="N12">
-        <v>22.924976</v>
+        <v>22.5574736</v>
       </c>
       <c r="O12">
-        <v>2.865622</v>
+        <v>2.8196842</v>
       </c>
       <c r="P12">
-        <v>20.059354</v>
+        <v>19.7377894</v>
       </c>
       <c r="Q12">
-        <v>68.65935400000001</v>
+        <v>68.33778940000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1098460229002942</v>
+        <v>0.1104836593109073</v>
       </c>
       <c r="T12">
-        <v>1.079907955999422</v>
+        <v>1.090659421924605</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.23804796921054</v>
+        <v>6.580043608373218</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2543,22 +2543,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1035568317867075</v>
+        <v>0.1036059929631502</v>
       </c>
       <c r="C13">
-        <v>612.4449061549603</v>
+        <v>605.1651106520213</v>
       </c>
       <c r="D13">
-        <v>601.7929061549603</v>
+        <v>601.2811106520213</v>
       </c>
       <c r="E13">
-        <v>30.248</v>
+        <v>37.01600000000001</v>
       </c>
       <c r="F13">
-        <v>74.44800000000001</v>
+        <v>81.21600000000001</v>
       </c>
       <c r="G13">
         <v>85.09999999999999</v>
@@ -2579,45 +2579,45 @@
         <v>26.6</v>
       </c>
       <c r="M13">
-        <v>4.042526400000001</v>
+        <v>4.4912448</v>
       </c>
       <c r="N13">
-        <v>22.5574736</v>
+        <v>22.1087552</v>
       </c>
       <c r="O13">
-        <v>2.8196842</v>
+        <v>2.7635944</v>
       </c>
       <c r="P13">
-        <v>19.7377894</v>
+        <v>19.3451608</v>
       </c>
       <c r="Q13">
-        <v>68.33778940000001</v>
+        <v>67.9451608</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1104836593109073</v>
+        <v>0.1111357874581252</v>
       </c>
       <c r="T13">
-        <v>1.090659421924605</v>
+        <v>1.101655239348087</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.580043608373218</v>
+        <v>5.922634188187649</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2625,22 +2625,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1036059929631502</v>
+        <v>0.1035589041395929</v>
       </c>
       <c r="C14">
-        <v>605.1651106520213</v>
+        <v>598.8873142067738</v>
       </c>
       <c r="D14">
-        <v>601.2811106520213</v>
+        <v>601.7713142067738</v>
       </c>
       <c r="E14">
-        <v>37.01600000000001</v>
+        <v>43.78400000000001</v>
       </c>
       <c r="F14">
-        <v>81.21600000000001</v>
+        <v>87.98400000000001</v>
       </c>
       <c r="G14">
         <v>85.09999999999999</v>
@@ -2661,28 +2661,28 @@
         <v>26.6</v>
       </c>
       <c r="M14">
-        <v>4.4912448</v>
+        <v>4.865515200000001</v>
       </c>
       <c r="N14">
-        <v>22.1087552</v>
+        <v>21.7344848</v>
       </c>
       <c r="O14">
-        <v>2.7635944</v>
+        <v>2.7168106</v>
       </c>
       <c r="P14">
-        <v>19.3451608</v>
+        <v>19.0176742</v>
       </c>
       <c r="Q14">
-        <v>67.9451608</v>
+        <v>67.61767420000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1111357874581252</v>
+        <v>0.1118029070570033</v>
       </c>
       <c r="T14">
-        <v>1.101655239348087</v>
+        <v>1.112903834183603</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.922634188187649</v>
+        <v>5.467046942942445</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2707,22 +2707,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1035589041395929</v>
+        <v>0.1035118153160356</v>
       </c>
       <c r="C15">
-        <v>598.8873142067738</v>
+        <v>592.6103177054741</v>
       </c>
       <c r="D15">
-        <v>601.7713142067738</v>
+        <v>602.2623177054742</v>
       </c>
       <c r="E15">
-        <v>43.78400000000001</v>
+        <v>50.55200000000002</v>
       </c>
       <c r="F15">
-        <v>87.98400000000001</v>
+        <v>94.75200000000002</v>
       </c>
       <c r="G15">
         <v>85.09999999999999</v>
@@ -2743,28 +2743,28 @@
         <v>26.6</v>
       </c>
       <c r="M15">
-        <v>4.865515200000001</v>
+        <v>5.239785600000001</v>
       </c>
       <c r="N15">
-        <v>21.7344848</v>
+        <v>21.3602144</v>
       </c>
       <c r="O15">
-        <v>2.7168106</v>
+        <v>2.6700268</v>
       </c>
       <c r="P15">
-        <v>19.0176742</v>
+        <v>18.6901876</v>
       </c>
       <c r="Q15">
-        <v>67.61767420000001</v>
+        <v>67.2901876</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1118029070570033</v>
+        <v>0.1124855410651577</v>
       </c>
       <c r="T15">
-        <v>1.112903834183603</v>
+        <v>1.124414024247853</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.467046942942445</v>
+        <v>5.076543589875127</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2789,22 +2789,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1035118153160356</v>
+        <v>0.1034647264924783</v>
       </c>
       <c r="C16">
-        <v>592.6103177054741</v>
+        <v>586.3341231078172</v>
       </c>
       <c r="D16">
-        <v>602.2623177054742</v>
+        <v>602.7541231078171</v>
       </c>
       <c r="E16">
-        <v>50.55200000000002</v>
+        <v>57.32000000000002</v>
       </c>
       <c r="F16">
-        <v>94.75200000000002</v>
+        <v>101.52</v>
       </c>
       <c r="G16">
         <v>85.09999999999999</v>
@@ -2825,28 +2825,28 @@
         <v>26.6</v>
       </c>
       <c r="M16">
-        <v>5.239785600000001</v>
+        <v>5.614056000000001</v>
       </c>
       <c r="N16">
-        <v>21.3602144</v>
+        <v>20.985944</v>
       </c>
       <c r="O16">
-        <v>2.6700268</v>
+        <v>2.623243</v>
       </c>
       <c r="P16">
-        <v>18.6901876</v>
+        <v>18.362701</v>
       </c>
       <c r="Q16">
-        <v>67.2901876</v>
+        <v>66.96270100000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1124855410651577</v>
+        <v>0.1131842370499745</v>
       </c>
       <c r="T16">
-        <v>1.124414024247853</v>
+        <v>1.136195042313614</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.076543589875127</v>
+        <v>4.738107350550118</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2871,22 +2871,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1034647264924783</v>
+        <v>0.103767637668921</v>
       </c>
       <c r="C17">
-        <v>586.3341231078176</v>
+        <v>576.416418067583</v>
       </c>
       <c r="D17">
-        <v>602.7541231078176</v>
+        <v>599.604418067583</v>
       </c>
       <c r="E17">
-        <v>57.32000000000001</v>
+        <v>64.08800000000001</v>
       </c>
       <c r="F17">
-        <v>101.52</v>
+        <v>108.288</v>
       </c>
       <c r="G17">
         <v>85.09999999999999</v>
@@ -2907,45 +2907,45 @@
         <v>26.6</v>
       </c>
       <c r="M17">
-        <v>5.614056000000001</v>
+        <v>6.259046400000001</v>
       </c>
       <c r="N17">
-        <v>20.985944</v>
+        <v>20.3409536</v>
       </c>
       <c r="O17">
-        <v>2.623243</v>
+        <v>2.5426192</v>
       </c>
       <c r="P17">
-        <v>18.362701</v>
+        <v>17.7983344</v>
       </c>
       <c r="Q17">
-        <v>66.96270100000001</v>
+        <v>66.3983344</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1131842370499744</v>
+        <v>0.1138995686534774</v>
       </c>
       <c r="T17">
-        <v>1.136195042313614</v>
+        <v>1.148256560809512</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.738107350550119</v>
+        <v>4.249848667042953</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2953,22 +2953,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.103767637668921</v>
+        <v>0.1042630488453637</v>
       </c>
       <c r="C18">
-        <v>576.416418067583</v>
+        <v>564.5674184272664</v>
       </c>
       <c r="D18">
-        <v>599.604418067583</v>
+        <v>594.5234184272664</v>
       </c>
       <c r="E18">
-        <v>64.08800000000001</v>
+        <v>70.85600000000002</v>
       </c>
       <c r="F18">
-        <v>108.288</v>
+        <v>115.056</v>
       </c>
       <c r="G18">
         <v>85.09999999999999</v>
@@ -2989,45 +2989,45 @@
         <v>26.6</v>
       </c>
       <c r="M18">
-        <v>6.259046400000001</v>
+        <v>7.052932800000002</v>
       </c>
       <c r="N18">
-        <v>20.3409536</v>
+        <v>19.5470672</v>
       </c>
       <c r="O18">
-        <v>2.5426192</v>
+        <v>2.4433834</v>
       </c>
       <c r="P18">
-        <v>17.7983344</v>
+        <v>17.1036838</v>
       </c>
       <c r="Q18">
-        <v>66.3983344</v>
+        <v>65.70368379999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1138995686534774</v>
+        <v>0.1146321371630888</v>
       </c>
       <c r="T18">
-        <v>1.148256560809512</v>
+        <v>1.160608718305311</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.249848667042953</v>
+        <v>3.771480709414954</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3035,22 +3035,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1042630488453637</v>
+        <v>0.1042684600218064</v>
       </c>
       <c r="C19">
-        <v>564.5674184272664</v>
+        <v>557.7443960935975</v>
       </c>
       <c r="D19">
-        <v>594.5234184272664</v>
+        <v>594.4683960935976</v>
       </c>
       <c r="E19">
-        <v>70.85600000000002</v>
+        <v>77.62400000000002</v>
       </c>
       <c r="F19">
-        <v>115.056</v>
+        <v>121.824</v>
       </c>
       <c r="G19">
         <v>85.09999999999999</v>
@@ -3071,28 +3071,28 @@
         <v>26.6</v>
       </c>
       <c r="M19">
-        <v>7.052932800000002</v>
+        <v>7.467811200000002</v>
       </c>
       <c r="N19">
-        <v>19.5470672</v>
+        <v>19.1321888</v>
       </c>
       <c r="O19">
-        <v>2.4433834</v>
+        <v>2.3915236</v>
       </c>
       <c r="P19">
-        <v>17.1036838</v>
+        <v>16.7406652</v>
       </c>
       <c r="Q19">
-        <v>65.70368379999999</v>
+        <v>65.3406652</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1146321371630888</v>
+        <v>0.1153825731973249</v>
       </c>
       <c r="T19">
-        <v>1.160608718305311</v>
+        <v>1.173262147935155</v>
       </c>
       <c r="U19">
         <v>0.0613</v>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.771480709414954</v>
+        <v>3.561954003336345</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3117,22 +3117,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1042684600218064</v>
+        <v>0.1047393711982491</v>
       </c>
       <c r="C20">
-        <v>557.7443960935975</v>
+        <v>546.2267388429149</v>
       </c>
       <c r="D20">
-        <v>594.4683960935974</v>
+        <v>589.7187388429148</v>
       </c>
       <c r="E20">
-        <v>77.62400000000001</v>
+        <v>84.39200000000001</v>
       </c>
       <c r="F20">
-        <v>121.824</v>
+        <v>128.592</v>
       </c>
       <c r="G20">
         <v>85.09999999999999</v>
@@ -3153,45 +3153,45 @@
         <v>26.6</v>
       </c>
       <c r="M20">
-        <v>7.467811200000001</v>
+        <v>8.242747200000002</v>
       </c>
       <c r="N20">
-        <v>19.1321888</v>
+        <v>18.3572528</v>
       </c>
       <c r="O20">
-        <v>2.3915236</v>
+        <v>2.2946566</v>
       </c>
       <c r="P20">
-        <v>16.7406652</v>
+        <v>16.0625962</v>
       </c>
       <c r="Q20">
-        <v>65.3406652</v>
+        <v>64.6625962</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1153825731973249</v>
+        <v>0.1161515385163569</v>
       </c>
       <c r="T20">
-        <v>1.173262147935155</v>
+        <v>1.186228007926228</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.561954003336345</v>
+        <v>3.22707943778744</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1047393711982491</v>
+        <v>0.1047692823746918</v>
       </c>
       <c r="C21">
-        <v>546.2267388429149</v>
+        <v>539.1596139334912</v>
       </c>
       <c r="D21">
-        <v>589.7187388429148</v>
+        <v>589.4196139334912</v>
       </c>
       <c r="E21">
-        <v>84.39200000000001</v>
+        <v>91.16000000000001</v>
       </c>
       <c r="F21">
-        <v>128.592</v>
+        <v>135.36</v>
       </c>
       <c r="G21">
         <v>85.09999999999999</v>
@@ -3235,28 +3235,28 @@
         <v>26.6</v>
       </c>
       <c r="M21">
-        <v>8.242747200000002</v>
+        <v>8.676576000000001</v>
       </c>
       <c r="N21">
-        <v>18.3572528</v>
+        <v>17.923424</v>
       </c>
       <c r="O21">
-        <v>2.2946566</v>
+        <v>2.240428</v>
       </c>
       <c r="P21">
-        <v>16.0625962</v>
+        <v>15.682996</v>
       </c>
       <c r="Q21">
-        <v>64.6625962</v>
+        <v>64.282996</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1161515385163569</v>
+        <v>0.1169397279683647</v>
       </c>
       <c r="T21">
-        <v>1.186228007926228</v>
+        <v>1.199518014417079</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.22707943778744</v>
+        <v>3.065725465898069</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3281,22 +3281,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1047692823746918</v>
+        <v>0.1062324435511345</v>
       </c>
       <c r="C22">
-        <v>539.1596139334912</v>
+        <v>518.1208705204501</v>
       </c>
       <c r="D22">
-        <v>589.4196139334912</v>
+        <v>575.1488705204501</v>
       </c>
       <c r="E22">
-        <v>91.16000000000001</v>
+        <v>97.92800000000001</v>
       </c>
       <c r="F22">
-        <v>135.36</v>
+        <v>142.128</v>
       </c>
       <c r="G22">
         <v>85.09999999999999</v>
@@ -3317,45 +3317,45 @@
         <v>26.6</v>
       </c>
       <c r="M22">
-        <v>8.676576000000001</v>
+        <v>10.2190032</v>
       </c>
       <c r="N22">
-        <v>17.923424</v>
+        <v>16.3809968</v>
       </c>
       <c r="O22">
-        <v>2.240428</v>
+        <v>2.0476246</v>
       </c>
       <c r="P22">
-        <v>15.682996</v>
+        <v>14.3333722</v>
       </c>
       <c r="Q22">
-        <v>64.282996</v>
+        <v>62.9333722</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1169397279683647</v>
+        <v>0.1177478715837146</v>
       </c>
       <c r="T22">
-        <v>1.199518014417079</v>
+        <v>1.213144476768458</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.065725465898069</v>
+        <v>2.602993607047701</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3363,22 +3363,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1062324435511345</v>
+        <v>0.1070813547275772</v>
       </c>
       <c r="C23">
-        <v>518.1208705204501</v>
+        <v>503.3855155807022</v>
       </c>
       <c r="D23">
-        <v>575.1488705204501</v>
+        <v>567.1815155807022</v>
       </c>
       <c r="E23">
-        <v>97.92800000000001</v>
+        <v>104.696</v>
       </c>
       <c r="F23">
-        <v>142.128</v>
+        <v>148.896</v>
       </c>
       <c r="G23">
         <v>85.09999999999999</v>
@@ -3399,45 +3399,45 @@
         <v>26.6</v>
       </c>
       <c r="M23">
-        <v>10.2190032</v>
+        <v>11.2863168</v>
       </c>
       <c r="N23">
-        <v>16.3809968</v>
+        <v>15.3136832</v>
       </c>
       <c r="O23">
-        <v>2.0476246</v>
+        <v>1.9142104</v>
       </c>
       <c r="P23">
-        <v>14.3333722</v>
+        <v>13.3994728</v>
       </c>
       <c r="Q23">
-        <v>62.9333722</v>
+        <v>61.9994728</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1177478715837146</v>
+        <v>0.1185767368302272</v>
       </c>
       <c r="T23">
-        <v>1.213144476768458</v>
+        <v>1.227120335590385</v>
       </c>
       <c r="U23">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.602993607047701</v>
+        <v>2.35683620009674</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3445,22 +3445,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1070813547275772</v>
+        <v>0.1072136409040199</v>
       </c>
       <c r="C24">
-        <v>503.3855155807022</v>
+        <v>495.3957955696318</v>
       </c>
       <c r="D24">
-        <v>567.1815155807022</v>
+        <v>565.9597955696318</v>
       </c>
       <c r="E24">
-        <v>104.696</v>
+        <v>111.464</v>
       </c>
       <c r="F24">
-        <v>148.896</v>
+        <v>155.664</v>
       </c>
       <c r="G24">
         <v>85.09999999999999</v>
@@ -3481,28 +3481,28 @@
         <v>26.6</v>
       </c>
       <c r="M24">
-        <v>11.2863168</v>
+        <v>11.7993312</v>
       </c>
       <c r="N24">
-        <v>15.3136832</v>
+        <v>14.8006688</v>
       </c>
       <c r="O24">
-        <v>1.9142104</v>
+        <v>1.8500836</v>
       </c>
       <c r="P24">
-        <v>13.3994728</v>
+        <v>12.9505852</v>
       </c>
       <c r="Q24">
-        <v>61.9994728</v>
+        <v>61.5505852</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1185767368302272</v>
+        <v>0.1194271310441817</v>
       </c>
       <c r="T24">
-        <v>1.227120335590385</v>
+        <v>1.241459203732362</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.35683620009674</v>
+        <v>2.254365060962099</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3527,22 +3527,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1072136409040199</v>
+        <v>0.1073459270804626</v>
       </c>
       <c r="C25">
-        <v>495.3957955696318</v>
+        <v>487.4113274631668</v>
       </c>
       <c r="D25">
-        <v>565.9597955696318</v>
+        <v>564.7433274631668</v>
       </c>
       <c r="E25">
-        <v>111.464</v>
+        <v>118.232</v>
       </c>
       <c r="F25">
-        <v>155.664</v>
+        <v>162.432</v>
       </c>
       <c r="G25">
         <v>85.09999999999999</v>
@@ -3563,28 +3563,28 @@
         <v>26.6</v>
       </c>
       <c r="M25">
-        <v>11.7993312</v>
+        <v>12.3123456</v>
       </c>
       <c r="N25">
-        <v>14.8006688</v>
+        <v>14.2876544</v>
       </c>
       <c r="O25">
-        <v>1.8500836</v>
+        <v>1.7859568</v>
       </c>
       <c r="P25">
-        <v>12.9505852</v>
+        <v>12.5016976</v>
       </c>
       <c r="Q25">
-        <v>61.5505852</v>
+        <v>61.1016976</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1194271310441817</v>
+        <v>0.1202999040532403</v>
       </c>
       <c r="T25">
-        <v>1.241459203732362</v>
+        <v>1.256175410509654</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.254365060962099</v>
+        <v>2.160433183422012</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3609,22 +3609,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1073459270804626</v>
+        <v>0.1074782132569053</v>
       </c>
       <c r="C26">
-        <v>487.4113274631668</v>
+        <v>479.4320774687731</v>
       </c>
       <c r="D26">
-        <v>564.7433274631668</v>
+        <v>563.5320774687731</v>
       </c>
       <c r="E26">
-        <v>118.232</v>
+        <v>125</v>
       </c>
       <c r="F26">
-        <v>162.432</v>
+        <v>169.2</v>
       </c>
       <c r="G26">
         <v>85.09999999999999</v>
@@ -3645,28 +3645,28 @@
         <v>26.6</v>
       </c>
       <c r="M26">
-        <v>12.3123456</v>
+        <v>12.82536</v>
       </c>
       <c r="N26">
-        <v>14.2876544</v>
+        <v>13.77464</v>
       </c>
       <c r="O26">
-        <v>1.7859568</v>
+        <v>1.72183</v>
       </c>
       <c r="P26">
-        <v>12.5016976</v>
+        <v>12.05281</v>
       </c>
       <c r="Q26">
-        <v>61.1016976</v>
+        <v>60.65281</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1202999040532403</v>
+        <v>0.1211959510092071</v>
       </c>
       <c r="T26">
-        <v>1.256175410509654</v>
+        <v>1.271284049467674</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.160433183422012</v>
+        <v>2.074015856085131</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3691,22 +3691,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1074782132569053</v>
+        <v>0.110840999433348</v>
       </c>
       <c r="C27">
-        <v>479.4320774687731</v>
+        <v>443.5280264147607</v>
       </c>
       <c r="D27">
-        <v>563.5320774687731</v>
+        <v>534.3960264147607</v>
       </c>
       <c r="E27">
-        <v>125</v>
+        <v>131.768</v>
       </c>
       <c r="F27">
-        <v>169.2</v>
+        <v>175.968</v>
       </c>
       <c r="G27">
         <v>85.09999999999999</v>
@@ -3727,45 +3727,45 @@
         <v>26.6</v>
       </c>
       <c r="M27">
-        <v>12.82536</v>
+        <v>15.83712</v>
       </c>
       <c r="N27">
-        <v>13.77464</v>
+        <v>10.76288</v>
       </c>
       <c r="O27">
-        <v>1.72183</v>
+        <v>1.34536</v>
       </c>
       <c r="P27">
-        <v>12.05281</v>
+        <v>9.417520000000001</v>
       </c>
       <c r="Q27">
-        <v>60.65281</v>
+        <v>58.01752</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1211959510092071</v>
+        <v>0.1221162154504703</v>
       </c>
       <c r="T27">
-        <v>1.271284049467674</v>
+        <v>1.286801030019154</v>
       </c>
       <c r="U27">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.074015856085131</v>
+        <v>1.679598310803985</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3773,22 +3773,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.110840999433348</v>
+        <v>0.1110975356097907</v>
       </c>
       <c r="C28">
-        <v>443.5280264147607</v>
+        <v>434.6605304377324</v>
       </c>
       <c r="D28">
-        <v>534.3960264147607</v>
+        <v>532.2965304377324</v>
       </c>
       <c r="E28">
-        <v>131.768</v>
+        <v>138.536</v>
       </c>
       <c r="F28">
-        <v>175.968</v>
+        <v>182.736</v>
       </c>
       <c r="G28">
         <v>85.09999999999999</v>
@@ -3809,28 +3809,28 @@
         <v>26.6</v>
       </c>
       <c r="M28">
-        <v>15.83712</v>
+        <v>16.44624</v>
       </c>
       <c r="N28">
-        <v>10.76288</v>
+        <v>10.15376</v>
       </c>
       <c r="O28">
-        <v>1.34536</v>
+        <v>1.26922</v>
       </c>
       <c r="P28">
-        <v>9.417520000000001</v>
+        <v>8.884540000000001</v>
       </c>
       <c r="Q28">
-        <v>58.01752</v>
+        <v>57.48454</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1221162154504703</v>
+        <v>0.1230616926161517</v>
       </c>
       <c r="T28">
-        <v>1.286801030019154</v>
+        <v>1.302743133325469</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.679598310803985</v>
+        <v>1.617390965959393</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3855,22 +3855,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1110975356097907</v>
+        <v>0.1113540717862334</v>
       </c>
       <c r="C29">
-        <v>434.6605304377324</v>
+        <v>425.8094665954511</v>
       </c>
       <c r="D29">
-        <v>532.2965304377324</v>
+        <v>530.2134665954511</v>
       </c>
       <c r="E29">
-        <v>138.536</v>
+        <v>145.304</v>
       </c>
       <c r="F29">
-        <v>182.736</v>
+        <v>189.504</v>
       </c>
       <c r="G29">
         <v>85.09999999999999</v>
@@ -3891,28 +3891,28 @@
         <v>26.6</v>
       </c>
       <c r="M29">
-        <v>16.44624</v>
+        <v>17.05536</v>
       </c>
       <c r="N29">
-        <v>10.15376</v>
+        <v>9.544639999999998</v>
       </c>
       <c r="O29">
-        <v>1.26922</v>
+        <v>1.19308</v>
       </c>
       <c r="P29">
-        <v>8.884540000000001</v>
+        <v>8.351559999999997</v>
       </c>
       <c r="Q29">
-        <v>57.48454</v>
+        <v>56.95156</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1230616926161517</v>
+        <v>0.1240334330364353</v>
       </c>
       <c r="T29">
-        <v>1.302743133325469</v>
+        <v>1.319128072834737</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.617390965959393</v>
+        <v>1.559627002889414</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3937,22 +3937,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1113540717862334</v>
+        <v>0.1116106079626761</v>
       </c>
       <c r="C30">
-        <v>425.8094665954511</v>
+        <v>416.974642725719</v>
       </c>
       <c r="D30">
-        <v>530.2134665954511</v>
+        <v>528.1466427257191</v>
       </c>
       <c r="E30">
-        <v>145.304</v>
+        <v>152.0720000000001</v>
       </c>
       <c r="F30">
-        <v>189.504</v>
+        <v>196.272</v>
       </c>
       <c r="G30">
         <v>85.09999999999999</v>
@@ -3973,28 +3973,28 @@
         <v>26.6</v>
       </c>
       <c r="M30">
-        <v>17.05536</v>
+        <v>17.66448</v>
       </c>
       <c r="N30">
-        <v>9.544639999999998</v>
+        <v>8.935519999999997</v>
       </c>
       <c r="O30">
-        <v>1.19308</v>
+        <v>1.11694</v>
       </c>
       <c r="P30">
-        <v>8.351559999999997</v>
+        <v>7.818579999999997</v>
       </c>
       <c r="Q30">
-        <v>56.95156</v>
+        <v>56.41858</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1240334330364353</v>
+        <v>0.1250325464263044</v>
       </c>
       <c r="T30">
-        <v>1.319128072834737</v>
+        <v>1.335974559935815</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.559627002889414</v>
+        <v>1.505846761410468</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4019,22 +4019,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1116106079626761</v>
+        <v>0.1276047814664082</v>
       </c>
       <c r="C31">
-        <v>416.9746427257194</v>
+        <v>306.9453310059696</v>
       </c>
       <c r="D31">
-        <v>528.1466427257194</v>
+        <v>424.8853310059697</v>
       </c>
       <c r="E31">
-        <v>152.072</v>
+        <v>158.84</v>
       </c>
       <c r="F31">
-        <v>196.272</v>
+        <v>203.04</v>
       </c>
       <c r="G31">
         <v>85.09999999999999</v>
@@ -4055,45 +4055,45 @@
         <v>26.6</v>
       </c>
       <c r="M31">
-        <v>17.66448</v>
+        <v>29.80627200000001</v>
       </c>
       <c r="N31">
-        <v>8.93552</v>
+        <v>-3.206272000000006</v>
       </c>
       <c r="O31">
-        <v>1.11694</v>
+        <v>-0.4007840000000007</v>
       </c>
       <c r="P31">
-        <v>7.818580000000001</v>
+        <v>-2.805488000000005</v>
       </c>
       <c r="Q31">
-        <v>56.41858000000001</v>
+        <v>45.794512</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1250325464263044</v>
+        <v>0.1263965807507284</v>
       </c>
       <c r="T31">
-        <v>1.335974559935815</v>
+        <v>1.35897413824679</v>
       </c>
       <c r="U31">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.125</v>
+        <v>0.1115537025227442</v>
       </c>
       <c r="W31">
-        <v>0.07875</v>
+        <v>0.1304239164696612</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.505846761410469</v>
+        <v>0.8924296201819535</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4101,22 +4101,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1276047814664082</v>
+        <v>0.1286147814664082</v>
       </c>
       <c r="C32">
-        <v>306.9453310059696</v>
+        <v>294.9954760675479</v>
       </c>
       <c r="D32">
-        <v>424.8853310059697</v>
+        <v>419.7034760675479</v>
       </c>
       <c r="E32">
-        <v>158.84</v>
+        <v>165.608</v>
       </c>
       <c r="F32">
-        <v>203.04</v>
+        <v>209.808</v>
       </c>
       <c r="G32">
         <v>85.09999999999999</v>
@@ -4137,37 +4137,37 @@
         <v>26.6</v>
       </c>
       <c r="M32">
-        <v>29.80627200000001</v>
+        <v>30.79981440000001</v>
       </c>
       <c r="N32">
-        <v>-3.206272000000006</v>
+        <v>-4.199814400000005</v>
       </c>
       <c r="O32">
-        <v>-0.4007840000000007</v>
+        <v>-0.5249768000000006</v>
       </c>
       <c r="P32">
-        <v>-2.805488000000005</v>
+        <v>-3.674837600000004</v>
       </c>
       <c r="Q32">
-        <v>45.794512</v>
+        <v>44.9251624</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1263965807507284</v>
+        <v>0.1275646471384201</v>
       </c>
       <c r="T32">
-        <v>1.35897413824679</v>
+        <v>1.378669415612686</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1115537025227442</v>
+        <v>0.1079551959897524</v>
       </c>
       <c r="W32">
-        <v>0.1304239164696612</v>
+        <v>0.1309521772287044</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8924296201819535</v>
+        <v>0.8636415679180196</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4183,22 +4183,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1286147814664082</v>
+        <v>0.1296247814664082</v>
       </c>
       <c r="C33">
-        <v>294.9954760675479</v>
+        <v>283.1704928769851</v>
       </c>
       <c r="D33">
-        <v>419.7034760675479</v>
+        <v>414.6464928769852</v>
       </c>
       <c r="E33">
-        <v>165.608</v>
+        <v>172.376</v>
       </c>
       <c r="F33">
-        <v>209.808</v>
+        <v>216.576</v>
       </c>
       <c r="G33">
         <v>85.09999999999999</v>
@@ -4219,37 +4219,37 @@
         <v>26.6</v>
       </c>
       <c r="M33">
-        <v>30.79981440000001</v>
+        <v>31.79335680000001</v>
       </c>
       <c r="N33">
-        <v>-4.199814400000005</v>
+        <v>-5.193356800000004</v>
       </c>
       <c r="O33">
-        <v>-0.5249768000000006</v>
+        <v>-0.6491696000000005</v>
       </c>
       <c r="P33">
-        <v>-3.674837600000004</v>
+        <v>-4.544187200000003</v>
       </c>
       <c r="Q33">
-        <v>44.9251624</v>
+        <v>44.0558128</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1275646471384201</v>
+        <v>0.1287670684198675</v>
       </c>
       <c r="T33">
-        <v>1.378669415612686</v>
+        <v>1.398943965842284</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1079551959897524</v>
+        <v>0.1045815961150727</v>
       </c>
       <c r="W33">
-        <v>0.1309521772287044</v>
+        <v>0.1314474216903073</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8636415679180196</v>
+        <v>0.8366527689205815</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1296247814664082</v>
+        <v>0.1306347814664082</v>
       </c>
       <c r="C34">
-        <v>283.1704928769851</v>
+        <v>271.4659214546659</v>
       </c>
       <c r="D34">
-        <v>414.6464928769852</v>
+        <v>409.709921454666</v>
       </c>
       <c r="E34">
-        <v>172.376</v>
+        <v>179.144</v>
       </c>
       <c r="F34">
-        <v>216.576</v>
+        <v>223.344</v>
       </c>
       <c r="G34">
         <v>85.09999999999999</v>
@@ -4301,37 +4301,37 @@
         <v>26.6</v>
       </c>
       <c r="M34">
-        <v>31.79335680000001</v>
+        <v>32.78689920000001</v>
       </c>
       <c r="N34">
-        <v>-5.193356800000004</v>
+        <v>-6.186899200000006</v>
       </c>
       <c r="O34">
-        <v>-0.6491696000000005</v>
+        <v>-0.7733624000000008</v>
       </c>
       <c r="P34">
-        <v>-4.544187200000003</v>
+        <v>-5.413536800000005</v>
       </c>
       <c r="Q34">
-        <v>44.0558128</v>
+        <v>43.1864632</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1287670684198675</v>
+        <v>0.1300053828738953</v>
       </c>
       <c r="T34">
-        <v>1.398943965842284</v>
+        <v>1.419823726526497</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1045815961150727</v>
+        <v>0.1014124568388584</v>
       </c>
       <c r="W34">
-        <v>0.1314474216903073</v>
+        <v>0.1319126513360556</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8366527689205815</v>
+        <v>0.8112996547108668</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4347,22 +4347,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1306347814664082</v>
+        <v>0.1505301122696837</v>
       </c>
       <c r="C35">
-        <v>271.4659214546659</v>
+        <v>186.8663003089285</v>
       </c>
       <c r="D35">
-        <v>409.709921454666</v>
+        <v>331.8783003089285</v>
       </c>
       <c r="E35">
-        <v>179.144</v>
+        <v>185.912</v>
       </c>
       <c r="F35">
-        <v>223.344</v>
+        <v>230.1120000000001</v>
       </c>
       <c r="G35">
         <v>85.09999999999999</v>
@@ -4383,45 +4383,45 @@
         <v>26.6</v>
       </c>
       <c r="M35">
-        <v>32.78689920000001</v>
+        <v>46.20648960000001</v>
       </c>
       <c r="N35">
-        <v>-6.186899200000006</v>
+        <v>-19.60648960000001</v>
       </c>
       <c r="O35">
-        <v>-0.7733624000000008</v>
+        <v>-2.450811200000001</v>
       </c>
       <c r="P35">
-        <v>-5.413536800000005</v>
+        <v>-17.15567840000001</v>
       </c>
       <c r="Q35">
-        <v>43.1864632</v>
+        <v>31.44432159999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1300053828738953</v>
+        <v>0.1320771777708868</v>
       </c>
       <c r="T35">
-        <v>1.419823726526497</v>
+        <v>1.454757164875091</v>
       </c>
       <c r="U35">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1014124568388584</v>
+        <v>0.07195958898379502</v>
       </c>
       <c r="W35">
-        <v>0.1319126513360556</v>
+        <v>0.186350514532054</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8112996547108668</v>
+        <v>0.5756767118703602</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4429,22 +4429,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1505301122696837</v>
+        <v>0.1520801122696836</v>
       </c>
       <c r="C36">
-        <v>186.8663003089285</v>
+        <v>175.2581533191179</v>
       </c>
       <c r="D36">
-        <v>331.8783003089285</v>
+        <v>327.038153319118</v>
       </c>
       <c r="E36">
-        <v>185.912</v>
+        <v>192.6800000000001</v>
       </c>
       <c r="F36">
-        <v>230.1120000000001</v>
+        <v>236.8800000000001</v>
       </c>
       <c r="G36">
         <v>85.09999999999999</v>
@@ -4465,37 +4465,37 @@
         <v>26.6</v>
       </c>
       <c r="M36">
-        <v>46.20648960000001</v>
+        <v>47.56550400000001</v>
       </c>
       <c r="N36">
-        <v>-19.60648960000001</v>
+        <v>-20.96550400000001</v>
       </c>
       <c r="O36">
-        <v>-2.450811200000001</v>
+        <v>-2.620688000000001</v>
       </c>
       <c r="P36">
-        <v>-17.15567840000001</v>
+        <v>-18.34481600000001</v>
       </c>
       <c r="Q36">
-        <v>31.44432159999999</v>
+        <v>30.25518399999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1320771777708868</v>
+        <v>0.133404518967362</v>
       </c>
       <c r="T36">
-        <v>1.454757164875091</v>
+        <v>1.477138044334708</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.07195958898379502</v>
+        <v>0.06990360072711517</v>
       </c>
       <c r="W36">
-        <v>0.186350514532054</v>
+        <v>0.1867633569739953</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5756767118703602</v>
+        <v>0.5592288058169214</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4511,22 +4511,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1520801122696836</v>
+        <v>0.1536301122696836</v>
       </c>
       <c r="C37">
-        <v>175.2581533191179</v>
+        <v>163.7891553606176</v>
       </c>
       <c r="D37">
-        <v>327.038153319118</v>
+        <v>322.3371553606177</v>
       </c>
       <c r="E37">
-        <v>192.6800000000001</v>
+        <v>199.448</v>
       </c>
       <c r="F37">
-        <v>236.8800000000001</v>
+        <v>243.6480000000001</v>
       </c>
       <c r="G37">
         <v>85.09999999999999</v>
@@ -4547,37 +4547,37 @@
         <v>26.6</v>
       </c>
       <c r="M37">
-        <v>47.56550400000001</v>
+        <v>48.92451840000001</v>
       </c>
       <c r="N37">
-        <v>-20.96550400000001</v>
+        <v>-22.32451840000001</v>
       </c>
       <c r="O37">
-        <v>-2.620688000000001</v>
+        <v>-2.790564800000001</v>
       </c>
       <c r="P37">
-        <v>-18.34481600000001</v>
+        <v>-19.53395360000001</v>
       </c>
       <c r="Q37">
-        <v>30.25518399999999</v>
+        <v>29.06604639999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.133404518967362</v>
+        <v>0.134773339576227</v>
       </c>
       <c r="T37">
-        <v>1.477138044334708</v>
+        <v>1.500218326277438</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.06990360072711517</v>
+        <v>0.06796183404025086</v>
       </c>
       <c r="W37">
-        <v>0.1867633569739953</v>
+        <v>0.1871532637247176</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5592288058169214</v>
+        <v>0.5436946723220069</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4593,22 +4593,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1536301122696836</v>
+        <v>0.1551801122696836</v>
       </c>
       <c r="C38">
-        <v>163.7891553606177</v>
+        <v>152.4533908882509</v>
       </c>
       <c r="D38">
-        <v>322.3371553606177</v>
+        <v>317.7693908882509</v>
       </c>
       <c r="E38">
-        <v>199.448</v>
+        <v>206.216</v>
       </c>
       <c r="F38">
-        <v>243.648</v>
+        <v>250.416</v>
       </c>
       <c r="G38">
         <v>85.09999999999999</v>
@@ -4629,37 +4629,37 @@
         <v>26.6</v>
       </c>
       <c r="M38">
-        <v>48.9245184</v>
+        <v>50.2835328</v>
       </c>
       <c r="N38">
-        <v>-22.3245184</v>
+        <v>-23.6835328</v>
       </c>
       <c r="O38">
-        <v>-2.7905648</v>
+        <v>-2.9604416</v>
       </c>
       <c r="P38">
-        <v>-19.5339536</v>
+        <v>-20.7230912</v>
       </c>
       <c r="Q38">
-        <v>29.0660464</v>
+        <v>27.8769088</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.134773339576227</v>
+        <v>0.1361856148075957</v>
       </c>
       <c r="T38">
-        <v>1.500218326277438</v>
+        <v>1.524031315583429</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.06796183404025087</v>
+        <v>0.06612502771483868</v>
       </c>
       <c r="W38">
-        <v>0.1871532637247176</v>
+        <v>0.1875220944348604</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.543694672322007</v>
+        <v>0.5290002217187095</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4675,22 +4675,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1551801122696836</v>
+        <v>0.1567301122696836</v>
       </c>
       <c r="C39">
-        <v>152.4533908882509</v>
+        <v>141.2452749828477</v>
       </c>
       <c r="D39">
-        <v>317.7693908882509</v>
+        <v>313.3292749828477</v>
       </c>
       <c r="E39">
-        <v>206.216</v>
+        <v>212.984</v>
       </c>
       <c r="F39">
-        <v>250.416</v>
+        <v>257.184</v>
       </c>
       <c r="G39">
         <v>85.09999999999999</v>
@@ -4711,37 +4711,37 @@
         <v>26.6</v>
       </c>
       <c r="M39">
-        <v>50.2835328</v>
+        <v>51.64254720000001</v>
       </c>
       <c r="N39">
-        <v>-23.6835328</v>
+        <v>-25.04254720000001</v>
       </c>
       <c r="O39">
-        <v>-2.9604416</v>
+        <v>-3.130318400000001</v>
       </c>
       <c r="P39">
-        <v>-20.7230912</v>
+        <v>-21.91222880000001</v>
       </c>
       <c r="Q39">
-        <v>27.8769088</v>
+        <v>26.68777119999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1361856148075957</v>
+        <v>0.1376434473044924</v>
       </c>
       <c r="T39">
-        <v>1.524031315583429</v>
+        <v>1.548612465834775</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.06612502771483868</v>
+        <v>0.06438489540655344</v>
       </c>
       <c r="W39">
-        <v>0.1875220944348604</v>
+        <v>0.1878715130023641</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5290002217187095</v>
+        <v>0.5150791632524276</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4757,22 +4757,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1567301122696836</v>
+        <v>0.1582801122696837</v>
       </c>
       <c r="C40">
-        <v>141.2452749828477</v>
+        <v>130.15953057076</v>
       </c>
       <c r="D40">
-        <v>313.3292749828477</v>
+        <v>309.01153057076</v>
       </c>
       <c r="E40">
-        <v>212.984</v>
+        <v>219.7520000000001</v>
       </c>
       <c r="F40">
-        <v>257.184</v>
+        <v>263.9520000000001</v>
       </c>
       <c r="G40">
         <v>85.09999999999999</v>
@@ -4793,37 +4793,37 @@
         <v>26.6</v>
       </c>
       <c r="M40">
-        <v>51.64254720000001</v>
+        <v>53.00156160000001</v>
       </c>
       <c r="N40">
-        <v>-25.04254720000001</v>
+        <v>-26.40156160000001</v>
       </c>
       <c r="O40">
-        <v>-3.130318400000001</v>
+        <v>-3.300195200000001</v>
       </c>
       <c r="P40">
-        <v>-21.91222880000001</v>
+        <v>-23.10136640000001</v>
       </c>
       <c r="Q40">
-        <v>26.68777119999999</v>
+        <v>25.49863359999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1376434473044924</v>
+        <v>0.1391490775881726</v>
       </c>
       <c r="T40">
-        <v>1.548612465834775</v>
+        <v>1.573999555438624</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.06438489540655344</v>
+        <v>0.06273400065253926</v>
       </c>
       <c r="W40">
-        <v>0.1878715130023641</v>
+        <v>0.1882030126689701</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5150791632524276</v>
+        <v>0.5018720052203141</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4839,22 +4839,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1582801122696837</v>
+        <v>0.1740420895940977</v>
       </c>
       <c r="C41">
-        <v>130.15953057076</v>
+        <v>85.41154480122862</v>
       </c>
       <c r="D41">
-        <v>309.01153057076</v>
+        <v>271.0315448012286</v>
       </c>
       <c r="E41">
-        <v>219.7520000000001</v>
+        <v>226.52</v>
       </c>
       <c r="F41">
-        <v>263.9520000000001</v>
+        <v>270.72</v>
       </c>
       <c r="G41">
         <v>85.09999999999999</v>
@@ -4875,45 +4875,45 @@
         <v>26.6</v>
       </c>
       <c r="M41">
-        <v>53.00156160000001</v>
+        <v>63.83577600000001</v>
       </c>
       <c r="N41">
-        <v>-26.40156160000001</v>
+        <v>-37.23577600000001</v>
       </c>
       <c r="O41">
-        <v>-3.300195200000001</v>
+        <v>-4.654472000000001</v>
       </c>
       <c r="P41">
-        <v>-23.10136640000001</v>
+        <v>-32.58130400000001</v>
       </c>
       <c r="Q41">
-        <v>25.49863359999999</v>
+        <v>16.01869599999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1391490775881726</v>
+        <v>0.1410581910886656</v>
       </c>
       <c r="T41">
-        <v>1.573999555438624</v>
+        <v>1.606189951730643</v>
       </c>
       <c r="U41">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06273400065253926</v>
+        <v>0.05208677967665028</v>
       </c>
       <c r="W41">
-        <v>0.1882030126689701</v>
+        <v>0.2235179373522459</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.5018720052203141</v>
+        <v>0.4166942374132022</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4921,22 +4921,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1740420895940977</v>
+        <v>0.1759420895940977</v>
       </c>
       <c r="C42">
-        <v>85.41154480122862</v>
+        <v>74.68663941628779</v>
       </c>
       <c r="D42">
-        <v>271.0315448012286</v>
+        <v>267.0746394162879</v>
       </c>
       <c r="E42">
-        <v>226.52</v>
+        <v>233.2880000000001</v>
       </c>
       <c r="F42">
-        <v>270.72</v>
+        <v>277.4880000000001</v>
       </c>
       <c r="G42">
         <v>85.09999999999999</v>
@@ -4957,37 +4957,37 @@
         <v>26.6</v>
       </c>
       <c r="M42">
-        <v>63.83577600000001</v>
+        <v>65.43167040000002</v>
       </c>
       <c r="N42">
-        <v>-37.23577600000001</v>
+        <v>-38.83167040000001</v>
       </c>
       <c r="O42">
-        <v>-4.654472000000001</v>
+        <v>-4.853958800000002</v>
       </c>
       <c r="P42">
-        <v>-32.58130400000001</v>
+        <v>-33.97771160000001</v>
       </c>
       <c r="Q42">
-        <v>16.01869599999999</v>
+        <v>14.62228839999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1410581910886656</v>
+        <v>0.1426727367003379</v>
       </c>
       <c r="T42">
-        <v>1.606189951730643</v>
+        <v>1.633413510234553</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05208677967665028</v>
+        <v>0.05081637041624417</v>
       </c>
       <c r="W42">
-        <v>0.2235179373522459</v>
+        <v>0.2238174998558496</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4166942374132022</v>
+        <v>0.4065309633299533</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5003,22 +5003,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1759420895940977</v>
+        <v>0.1778420895940977</v>
       </c>
       <c r="C43">
-        <v>74.68663941628779</v>
+        <v>64.07560863382406</v>
       </c>
       <c r="D43">
-        <v>267.0746394162879</v>
+        <v>263.2316086338241</v>
       </c>
       <c r="E43">
-        <v>233.2880000000001</v>
+        <v>240.056</v>
       </c>
       <c r="F43">
-        <v>277.4880000000001</v>
+        <v>284.256</v>
       </c>
       <c r="G43">
         <v>85.09999999999999</v>
@@ -5039,37 +5039,37 @@
         <v>26.6</v>
       </c>
       <c r="M43">
-        <v>65.43167040000002</v>
+        <v>67.02756480000001</v>
       </c>
       <c r="N43">
-        <v>-38.83167040000001</v>
+        <v>-40.42756480000001</v>
       </c>
       <c r="O43">
-        <v>-4.853958800000002</v>
+        <v>-5.053445600000001</v>
       </c>
       <c r="P43">
-        <v>-33.97771160000001</v>
+        <v>-35.3741192</v>
       </c>
       <c r="Q43">
-        <v>14.62228839999999</v>
+        <v>13.2258808</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1426727367003379</v>
+        <v>0.1443429562986196</v>
       </c>
       <c r="T43">
-        <v>1.633413510234553</v>
+        <v>1.661575812135149</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05081637041624417</v>
+        <v>0.04960645683490503</v>
       </c>
       <c r="W43">
-        <v>0.2238174998558496</v>
+        <v>0.2241027974783294</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4065309633299533</v>
+        <v>0.3968516546792402</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5085,22 +5085,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1778420895940977</v>
+        <v>0.1797420895940977</v>
       </c>
       <c r="C44">
-        <v>64.07560863382406</v>
+        <v>53.57360643989159</v>
       </c>
       <c r="D44">
-        <v>263.2316086338241</v>
+        <v>259.4976064398916</v>
       </c>
       <c r="E44">
-        <v>240.056</v>
+        <v>246.824</v>
       </c>
       <c r="F44">
-        <v>284.256</v>
+        <v>291.024</v>
       </c>
       <c r="G44">
         <v>85.09999999999999</v>
@@ -5121,37 +5121,37 @@
         <v>26.6</v>
       </c>
       <c r="M44">
-        <v>67.02756480000001</v>
+        <v>68.6234592</v>
       </c>
       <c r="N44">
-        <v>-40.42756480000001</v>
+        <v>-42.0234592</v>
       </c>
       <c r="O44">
-        <v>-5.053445600000001</v>
+        <v>-5.2529324</v>
       </c>
       <c r="P44">
-        <v>-35.3741192</v>
+        <v>-36.7705268</v>
       </c>
       <c r="Q44">
-        <v>13.2258808</v>
+        <v>11.8294732</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1443429562986196</v>
+        <v>0.1460717800933322</v>
       </c>
       <c r="T44">
-        <v>1.661575812135148</v>
+        <v>1.690726264979625</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04960645683490503</v>
+        <v>0.04845281830386073</v>
       </c>
       <c r="W44">
-        <v>0.2241027974783294</v>
+        <v>0.2243748254439497</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3968516546792402</v>
+        <v>0.3876225464308859</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5167,22 +5167,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1797420895940977</v>
+        <v>0.1816420895940977</v>
       </c>
       <c r="C45">
-        <v>53.57360643989159</v>
+        <v>43.17605794200676</v>
       </c>
       <c r="D45">
-        <v>259.4976064398916</v>
+        <v>255.8680579420068</v>
       </c>
       <c r="E45">
-        <v>246.824</v>
+        <v>253.592</v>
       </c>
       <c r="F45">
-        <v>291.024</v>
+        <v>297.792</v>
       </c>
       <c r="G45">
         <v>85.09999999999999</v>
@@ -5203,37 +5203,37 @@
         <v>26.6</v>
       </c>
       <c r="M45">
-        <v>68.6234592</v>
+        <v>70.21935360000001</v>
       </c>
       <c r="N45">
-        <v>-42.0234592</v>
+        <v>-43.6193536</v>
       </c>
       <c r="O45">
-        <v>-5.2529324</v>
+        <v>-5.4524192</v>
       </c>
       <c r="P45">
-        <v>-36.7705268</v>
+        <v>-38.1669344</v>
       </c>
       <c r="Q45">
-        <v>11.8294732</v>
+        <v>10.4330656</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1460717800933322</v>
+        <v>0.1478623475949989</v>
       </c>
       <c r="T45">
-        <v>1.690726264979625</v>
+        <v>1.72091780542569</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04845281830386073</v>
+        <v>0.04735161788786389</v>
       </c>
       <c r="W45">
-        <v>0.2243748254439497</v>
+        <v>0.2246344885020417</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3876225464308859</v>
+        <v>0.3788129431029111</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5249,22 +5249,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1816420895940977</v>
+        <v>0.1835420895940977</v>
       </c>
       <c r="C46">
-        <v>43.17605794200676</v>
+        <v>32.87864067004273</v>
       </c>
       <c r="D46">
-        <v>255.8680579420068</v>
+        <v>252.3386406700428</v>
       </c>
       <c r="E46">
-        <v>253.592</v>
+        <v>260.3600000000001</v>
       </c>
       <c r="F46">
-        <v>297.792</v>
+        <v>304.5600000000001</v>
       </c>
       <c r="G46">
         <v>85.09999999999999</v>
@@ -5285,37 +5285,37 @@
         <v>26.6</v>
       </c>
       <c r="M46">
-        <v>70.21935360000001</v>
+        <v>71.81524800000001</v>
       </c>
       <c r="N46">
-        <v>-43.6193536</v>
+        <v>-45.21524800000001</v>
       </c>
       <c r="O46">
-        <v>-5.4524192</v>
+        <v>-5.651906000000001</v>
       </c>
       <c r="P46">
-        <v>-38.1669344</v>
+        <v>-39.56334200000001</v>
       </c>
       <c r="Q46">
-        <v>10.4330656</v>
+        <v>9.036657999999996</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1478623475949989</v>
+        <v>0.1497180266421806</v>
       </c>
       <c r="T46">
-        <v>1.72091780542569</v>
+        <v>1.752207220069793</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04735161788786389</v>
+        <v>0.04629935971257803</v>
       </c>
       <c r="W46">
-        <v>0.2246344885020417</v>
+        <v>0.2248826109797741</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3788129431029111</v>
+        <v>0.3703948777006242</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1835420895940977</v>
+        <v>0.1854420895940977</v>
       </c>
       <c r="C47">
-        <v>32.87864067004273</v>
+        <v>22.67726740366805</v>
       </c>
       <c r="D47">
-        <v>252.3386406700428</v>
+        <v>248.9052674036681</v>
       </c>
       <c r="E47">
-        <v>260.3600000000001</v>
+        <v>267.128</v>
       </c>
       <c r="F47">
-        <v>304.5600000000001</v>
+        <v>311.328</v>
       </c>
       <c r="G47">
         <v>85.09999999999999</v>
@@ -5367,37 +5367,37 @@
         <v>26.6</v>
       </c>
       <c r="M47">
-        <v>71.81524800000001</v>
+        <v>73.41114240000002</v>
       </c>
       <c r="N47">
-        <v>-45.21524800000001</v>
+        <v>-46.81114240000002</v>
       </c>
       <c r="O47">
-        <v>-5.651906000000001</v>
+        <v>-5.851392800000002</v>
       </c>
       <c r="P47">
-        <v>-39.56334200000001</v>
+        <v>-40.95974960000002</v>
       </c>
       <c r="Q47">
-        <v>9.036657999999996</v>
+        <v>7.640250399999985</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1497180266421806</v>
+        <v>0.1516424345429618</v>
       </c>
       <c r="T47">
-        <v>1.752207220069793</v>
+        <v>1.784655501922938</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04629935971257803</v>
+        <v>0.04529285189273937</v>
       </c>
       <c r="W47">
-        <v>0.2248826109797741</v>
+        <v>0.2251199455236921</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3703948777006242</v>
+        <v>0.3623428151419149</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5413,22 +5413,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1854420895940977</v>
+        <v>0.1873420895940977</v>
       </c>
       <c r="C48">
-        <v>22.67726740366805</v>
+        <v>12.56807038288667</v>
       </c>
       <c r="D48">
-        <v>248.9052674036681</v>
+        <v>245.5640703828867</v>
       </c>
       <c r="E48">
-        <v>267.128</v>
+        <v>273.8960000000001</v>
       </c>
       <c r="F48">
-        <v>311.328</v>
+        <v>318.0960000000001</v>
       </c>
       <c r="G48">
         <v>85.09999999999999</v>
@@ -5449,37 +5449,37 @@
         <v>26.6</v>
       </c>
       <c r="M48">
-        <v>73.41114240000002</v>
+        <v>75.00703680000002</v>
       </c>
       <c r="N48">
-        <v>-46.81114240000002</v>
+        <v>-48.40703680000002</v>
       </c>
       <c r="O48">
-        <v>-5.851392800000002</v>
+        <v>-6.050879600000003</v>
       </c>
       <c r="P48">
-        <v>-40.95974960000002</v>
+        <v>-42.35615720000002</v>
       </c>
       <c r="Q48">
-        <v>7.640250399999985</v>
+        <v>6.243842799999982</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1516424345429618</v>
+        <v>0.1536394616098101</v>
       </c>
       <c r="T48">
-        <v>1.784655501922938</v>
+        <v>1.818328247242238</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04529285189273937</v>
+        <v>0.04432917419289385</v>
       </c>
       <c r="W48">
-        <v>0.2251199455236921</v>
+        <v>0.2253471807253156</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3623428151419149</v>
+        <v>0.3546333935431508</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5495,22 +5495,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1873420895940977</v>
+        <v>0.1892420895940977</v>
       </c>
       <c r="C49">
-        <v>12.56807038288667</v>
+        <v>2.54738677344011</v>
       </c>
       <c r="D49">
-        <v>245.5640703828867</v>
+        <v>242.3113867734401</v>
       </c>
       <c r="E49">
-        <v>273.8960000000001</v>
+        <v>280.664</v>
       </c>
       <c r="F49">
-        <v>318.0960000000001</v>
+        <v>324.864</v>
       </c>
       <c r="G49">
         <v>85.09999999999999</v>
@@ -5531,37 +5531,37 @@
         <v>26.6</v>
       </c>
       <c r="M49">
-        <v>75.00703680000002</v>
+        <v>76.60293120000001</v>
       </c>
       <c r="N49">
-        <v>-48.40703680000002</v>
+        <v>-50.00293120000001</v>
       </c>
       <c r="O49">
-        <v>-6.050879600000003</v>
+        <v>-6.250366400000002</v>
       </c>
       <c r="P49">
-        <v>-42.35615720000002</v>
+        <v>-43.75256480000001</v>
       </c>
       <c r="Q49">
-        <v>6.243842799999982</v>
+        <v>4.847435199999993</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1536394616098101</v>
+        <v>0.1557132974099988</v>
       </c>
       <c r="T49">
-        <v>1.818328247242238</v>
+        <v>1.853296098150743</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04432917419289385</v>
+        <v>0.0434056497305419</v>
       </c>
       <c r="W49">
-        <v>0.2253471807253156</v>
+        <v>0.2255649477935382</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3546333935431508</v>
+        <v>0.3472451978443352</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5577,22 +5577,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1892420895940977</v>
+        <v>0.1911420895940977</v>
       </c>
       <c r="C50">
-        <v>2.54738677344011</v>
+        <v>-7.388254727760739</v>
       </c>
       <c r="D50">
-        <v>242.3113867734401</v>
+        <v>239.1437452722392</v>
       </c>
       <c r="E50">
-        <v>280.664</v>
+        <v>287.432</v>
       </c>
       <c r="F50">
-        <v>324.864</v>
+        <v>331.632</v>
       </c>
       <c r="G50">
         <v>85.09999999999999</v>
@@ -5613,37 +5613,37 @@
         <v>26.6</v>
       </c>
       <c r="M50">
-        <v>76.60293120000001</v>
+        <v>78.19882560000001</v>
       </c>
       <c r="N50">
-        <v>-50.00293120000001</v>
+        <v>-51.5988256</v>
       </c>
       <c r="O50">
-        <v>-6.250366400000002</v>
+        <v>-6.449853200000001</v>
       </c>
       <c r="P50">
-        <v>-43.75256480000001</v>
+        <v>-45.14897240000001</v>
       </c>
       <c r="Q50">
-        <v>4.847435199999993</v>
+        <v>3.451027599999996</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1557132974099988</v>
+        <v>0.1578684601043125</v>
       </c>
       <c r="T50">
-        <v>1.853296098150743</v>
+        <v>1.889635237330169</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0434056497305419</v>
+        <v>0.04251982014420431</v>
       </c>
       <c r="W50">
-        <v>0.2255649477935382</v>
+        <v>0.2257738264099966</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3472451978443352</v>
+        <v>0.3401585611536345</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5659,22 +5659,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1911420895940977</v>
+        <v>0.1930420895940977</v>
       </c>
       <c r="C51">
-        <v>-7.388254727760739</v>
+        <v>-17.2421462501498</v>
       </c>
       <c r="D51">
-        <v>239.1437452722392</v>
+        <v>236.0578537498503</v>
       </c>
       <c r="E51">
-        <v>287.432</v>
+        <v>294.2</v>
       </c>
       <c r="F51">
-        <v>331.632</v>
+        <v>338.4</v>
       </c>
       <c r="G51">
         <v>85.09999999999999</v>
@@ -5695,37 +5695,37 @@
         <v>26.6</v>
       </c>
       <c r="M51">
-        <v>78.19882560000001</v>
+        <v>79.79472000000001</v>
       </c>
       <c r="N51">
-        <v>-51.5988256</v>
+        <v>-53.19472000000001</v>
       </c>
       <c r="O51">
-        <v>-6.449853200000001</v>
+        <v>-6.649340000000001</v>
       </c>
       <c r="P51">
-        <v>-45.14897240000001</v>
+        <v>-46.54538000000001</v>
       </c>
       <c r="Q51">
-        <v>3.451027599999996</v>
+        <v>2.054619999999993</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1578684601043125</v>
+        <v>0.1601098293063987</v>
       </c>
       <c r="T51">
-        <v>1.889635237330169</v>
+        <v>1.927427942076772</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04251982014420431</v>
+        <v>0.04166942374132022</v>
       </c>
       <c r="W51">
-        <v>0.2257738264099966</v>
+        <v>0.2259743498817967</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3401585611536345</v>
+        <v>0.3333553899305618</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5741,22 +5741,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1930420895940977</v>
+        <v>0.1949420895940977</v>
       </c>
       <c r="C52">
-        <v>-17.2421462501498</v>
+        <v>-27.01741216244437</v>
       </c>
       <c r="D52">
-        <v>236.0578537498503</v>
+        <v>233.0505878375557</v>
       </c>
       <c r="E52">
-        <v>294.2</v>
+        <v>300.9680000000001</v>
       </c>
       <c r="F52">
-        <v>338.4</v>
+        <v>345.1680000000001</v>
       </c>
       <c r="G52">
         <v>85.09999999999999</v>
@@ -5777,37 +5777,37 @@
         <v>26.6</v>
       </c>
       <c r="M52">
-        <v>79.79472000000001</v>
+        <v>81.39061440000002</v>
       </c>
       <c r="N52">
-        <v>-53.19472000000001</v>
+        <v>-54.79061440000002</v>
       </c>
       <c r="O52">
-        <v>-6.649340000000001</v>
+        <v>-6.848826800000002</v>
       </c>
       <c r="P52">
-        <v>-46.54538000000001</v>
+        <v>-47.94178760000001</v>
       </c>
       <c r="Q52">
-        <v>2.054619999999993</v>
+        <v>0.6582123999999894</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1601098293063987</v>
+        <v>0.162442682965713</v>
       </c>
       <c r="T52">
-        <v>1.927427942076772</v>
+        <v>1.966763206200788</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04166942374132022</v>
+        <v>0.04085237621698061</v>
       </c>
       <c r="W52">
-        <v>0.2259743498817967</v>
+        <v>0.226167009688036</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3333553899305618</v>
+        <v>0.3268190097358449</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5823,22 +5823,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1949420895940977</v>
+        <v>0.1968420895940977</v>
       </c>
       <c r="C53">
-        <v>-27.01741216244437</v>
+        <v>-36.71701962418763</v>
       </c>
       <c r="D53">
-        <v>233.0505878375557</v>
+        <v>230.1189803758124</v>
       </c>
       <c r="E53">
-        <v>300.9680000000001</v>
+        <v>307.736</v>
       </c>
       <c r="F53">
-        <v>345.1680000000001</v>
+        <v>351.936</v>
       </c>
       <c r="G53">
         <v>85.09999999999999</v>
@@ -5859,37 +5859,37 @@
         <v>26.6</v>
       </c>
       <c r="M53">
-        <v>81.39061440000002</v>
+        <v>82.98650880000001</v>
       </c>
       <c r="N53">
-        <v>-54.79061440000002</v>
+        <v>-56.38650880000001</v>
       </c>
       <c r="O53">
-        <v>-6.848826800000002</v>
+        <v>-7.048313600000001</v>
       </c>
       <c r="P53">
-        <v>-47.94178760000001</v>
+        <v>-49.33819520000001</v>
       </c>
       <c r="Q53">
-        <v>0.6582123999999894</v>
+        <v>-0.7381952000000069</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.162442682965713</v>
+        <v>0.164872738860832</v>
       </c>
       <c r="T53">
-        <v>1.966763206200788</v>
+        <v>2.007737439663305</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04085237621698061</v>
+        <v>0.04006675359742329</v>
       </c>
       <c r="W53">
-        <v>0.226167009688036</v>
+        <v>0.2263522595017276</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3268190097358449</v>
+        <v>0.3205340287793863</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5905,22 +5905,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1968420895940977</v>
+        <v>0.1987420895940977</v>
       </c>
       <c r="C54">
-        <v>-36.71701962418763</v>
+        <v>-46.34378835079804</v>
       </c>
       <c r="D54">
-        <v>230.1189803758124</v>
+        <v>227.2602116492021</v>
       </c>
       <c r="E54">
-        <v>307.736</v>
+        <v>314.5040000000001</v>
       </c>
       <c r="F54">
-        <v>351.936</v>
+        <v>358.7040000000001</v>
       </c>
       <c r="G54">
         <v>85.09999999999999</v>
@@ -5941,37 +5941,37 @@
         <v>26.6</v>
       </c>
       <c r="M54">
-        <v>82.98650880000001</v>
+        <v>84.58240320000002</v>
       </c>
       <c r="N54">
-        <v>-56.38650880000001</v>
+        <v>-57.98240320000001</v>
       </c>
       <c r="O54">
-        <v>-7.048313600000001</v>
+        <v>-7.247800400000002</v>
       </c>
       <c r="P54">
-        <v>-49.33819520000001</v>
+        <v>-50.73460280000001</v>
       </c>
       <c r="Q54">
-        <v>-0.7381952000000069</v>
+        <v>-2.13460280000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.164872738860832</v>
+        <v>0.1674062013897859</v>
       </c>
       <c r="T54">
-        <v>2.007737439663305</v>
+        <v>2.050455257528482</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04006675359742329</v>
+        <v>0.03931077711445304</v>
       </c>
       <c r="W54">
-        <v>0.2263522595017276</v>
+        <v>0.226530518756412</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3205340287793863</v>
+        <v>0.3144862169156243</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5987,22 +5987,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1987420895940977</v>
+        <v>0.2006420895940977</v>
       </c>
       <c r="C55">
-        <v>-46.34378835079804</v>
+        <v>-55.90039965968293</v>
       </c>
       <c r="D55">
-        <v>227.2602116492021</v>
+        <v>224.4716003403171</v>
       </c>
       <c r="E55">
-        <v>314.5040000000001</v>
+        <v>321.272</v>
       </c>
       <c r="F55">
-        <v>358.7040000000001</v>
+        <v>365.472</v>
       </c>
       <c r="G55">
         <v>85.09999999999999</v>
@@ -6023,37 +6023,37 @@
         <v>26.6</v>
       </c>
       <c r="M55">
-        <v>84.58240320000002</v>
+        <v>86.17829760000001</v>
       </c>
       <c r="N55">
-        <v>-57.98240320000001</v>
+        <v>-59.57829760000001</v>
       </c>
       <c r="O55">
-        <v>-7.247800400000002</v>
+        <v>-7.447287200000001</v>
       </c>
       <c r="P55">
-        <v>-50.73460280000001</v>
+        <v>-52.13101040000001</v>
       </c>
       <c r="Q55">
-        <v>-2.13460280000001</v>
+        <v>-3.531010400000007</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1674062013897859</v>
+        <v>0.1700498144634768</v>
       </c>
       <c r="T55">
-        <v>2.050455257528482</v>
+        <v>2.095030371822578</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03931077711445304</v>
+        <v>0.03858279976048169</v>
       </c>
       <c r="W55">
-        <v>0.226530518756412</v>
+        <v>0.2267021758164784</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3144862169156243</v>
+        <v>0.3086623980838535</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6069,22 +6069,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2006420895940977</v>
+        <v>0.2025420895940977</v>
       </c>
       <c r="C56">
-        <v>-55.90039965968293</v>
+        <v>-65.38940485842107</v>
       </c>
       <c r="D56">
-        <v>224.4716003403171</v>
+        <v>221.750595141579</v>
       </c>
       <c r="E56">
-        <v>321.272</v>
+        <v>328.0400000000001</v>
       </c>
       <c r="F56">
-        <v>365.472</v>
+        <v>372.2400000000001</v>
       </c>
       <c r="G56">
         <v>85.09999999999999</v>
@@ -6105,37 +6105,37 @@
         <v>26.6</v>
       </c>
       <c r="M56">
-        <v>86.17829760000001</v>
+        <v>87.77419200000001</v>
       </c>
       <c r="N56">
-        <v>-59.57829760000001</v>
+        <v>-61.17419200000001</v>
       </c>
       <c r="O56">
-        <v>-7.447287200000001</v>
+        <v>-7.646774000000002</v>
       </c>
       <c r="P56">
-        <v>-52.13101040000001</v>
+        <v>-53.52741800000001</v>
       </c>
       <c r="Q56">
-        <v>-3.531010400000007</v>
+        <v>-4.92741800000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1700498144634768</v>
+        <v>0.1728109214515542</v>
       </c>
       <c r="T56">
-        <v>2.095030371822578</v>
+        <v>2.141586602307525</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03858279976048169</v>
+        <v>0.03788129431029112</v>
       </c>
       <c r="W56">
-        <v>0.2267021758164784</v>
+        <v>0.2268675908016334</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3086623980838535</v>
+        <v>0.3030503544823289</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6151,22 +6151,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2025420895940977</v>
+        <v>0.2044420895940977</v>
       </c>
       <c r="C57">
-        <v>-65.38940485842107</v>
+        <v>-74.81323303016921</v>
       </c>
       <c r="D57">
-        <v>221.750595141579</v>
+        <v>219.0947669698309</v>
       </c>
       <c r="E57">
-        <v>328.0400000000001</v>
+        <v>334.8080000000001</v>
       </c>
       <c r="F57">
-        <v>372.2400000000001</v>
+        <v>379.0080000000001</v>
       </c>
       <c r="G57">
         <v>85.09999999999999</v>
@@ -6187,37 +6187,37 @@
         <v>26.6</v>
       </c>
       <c r="M57">
-        <v>87.77419200000001</v>
+        <v>89.37008640000002</v>
       </c>
       <c r="N57">
-        <v>-61.17419200000001</v>
+        <v>-62.77008640000002</v>
       </c>
       <c r="O57">
-        <v>-7.646774000000002</v>
+        <v>-7.846260800000002</v>
       </c>
       <c r="P57">
-        <v>-53.52741800000001</v>
+        <v>-54.92382560000001</v>
       </c>
       <c r="Q57">
-        <v>-4.92741800000001</v>
+        <v>-6.323825600000013</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1728109214515542</v>
+        <v>0.1756975333027258</v>
       </c>
       <c r="T57">
-        <v>2.141586602307525</v>
+        <v>2.190259025087242</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03788129431029112</v>
+        <v>0.03720484262617877</v>
       </c>
       <c r="W57">
-        <v>0.2268675908016334</v>
+        <v>0.227027098108747</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3030503544823289</v>
+        <v>0.2976387410094301</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6233,22 +6233,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2044420895940977</v>
+        <v>0.2063420895940977</v>
       </c>
       <c r="C58">
-        <v>-74.81323303016921</v>
+        <v>-84.17419826623393</v>
       </c>
       <c r="D58">
-        <v>219.0947669698309</v>
+        <v>216.5018017337661</v>
       </c>
       <c r="E58">
-        <v>334.8080000000001</v>
+        <v>341.5760000000001</v>
       </c>
       <c r="F58">
-        <v>379.0080000000001</v>
+        <v>385.7760000000001</v>
       </c>
       <c r="G58">
         <v>85.09999999999999</v>
@@ -6269,37 +6269,37 @@
         <v>26.6</v>
       </c>
       <c r="M58">
-        <v>89.37008640000002</v>
+        <v>90.96598080000003</v>
       </c>
       <c r="N58">
-        <v>-62.77008640000002</v>
+        <v>-64.36598080000002</v>
       </c>
       <c r="O58">
-        <v>-7.846260800000002</v>
+        <v>-8.045747600000002</v>
       </c>
       <c r="P58">
-        <v>-54.92382560000001</v>
+        <v>-56.32023320000002</v>
       </c>
       <c r="Q58">
-        <v>-6.323825600000013</v>
+        <v>-7.720233200000017</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1756975333027258</v>
+        <v>0.1787184061702311</v>
       </c>
       <c r="T58">
-        <v>2.190259025087242</v>
+        <v>2.241195281484619</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03720484262617877</v>
+        <v>0.03655212608887738</v>
       </c>
       <c r="W58">
-        <v>0.227027098108747</v>
+        <v>0.2271810086682427</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2976387410094301</v>
+        <v>0.2924170087110192</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6315,22 +6315,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2063420895940977</v>
+        <v>0.2082420895940977</v>
       </c>
       <c r="C59">
-        <v>-84.17419826623393</v>
+        <v>-93.47450639106796</v>
       </c>
       <c r="D59">
-        <v>216.5018017337661</v>
+        <v>213.9694936089321</v>
       </c>
       <c r="E59">
-        <v>341.5760000000001</v>
+        <v>348.3440000000001</v>
       </c>
       <c r="F59">
-        <v>385.7760000000001</v>
+        <v>392.5440000000001</v>
       </c>
       <c r="G59">
         <v>85.09999999999999</v>
@@ -6351,37 +6351,37 @@
         <v>26.6</v>
       </c>
       <c r="M59">
-        <v>90.96598080000003</v>
+        <v>92.56187520000003</v>
       </c>
       <c r="N59">
-        <v>-64.36598080000002</v>
+        <v>-65.96187520000004</v>
       </c>
       <c r="O59">
-        <v>-8.045747600000002</v>
+        <v>-8.245234400000005</v>
       </c>
       <c r="P59">
-        <v>-56.32023320000002</v>
+        <v>-57.71664080000004</v>
       </c>
       <c r="Q59">
-        <v>-7.720233200000017</v>
+        <v>-9.116640800000035</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1787184061702311</v>
+        <v>0.1818831301266652</v>
       </c>
       <c r="T59">
-        <v>2.241195281484619</v>
+        <v>2.29455707390092</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03655212608887738</v>
+        <v>0.0359219170183795</v>
       </c>
       <c r="W59">
-        <v>0.2271810086682427</v>
+        <v>0.2273296119670661</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2924170087110192</v>
+        <v>0.2873753361470359</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2082420895940977</v>
+        <v>0.2101420895940977</v>
       </c>
       <c r="C60">
-        <v>-93.47450639106791</v>
+        <v>-102.7162612207715</v>
       </c>
       <c r="D60">
-        <v>213.9694936089321</v>
+        <v>211.4957387792286</v>
       </c>
       <c r="E60">
-        <v>348.3440000000001</v>
+        <v>355.112</v>
       </c>
       <c r="F60">
-        <v>392.544</v>
+        <v>399.312</v>
       </c>
       <c r="G60">
         <v>85.09999999999999</v>
@@ -6433,37 +6433,37 @@
         <v>26.6</v>
       </c>
       <c r="M60">
-        <v>92.56187520000002</v>
+        <v>94.15776960000001</v>
       </c>
       <c r="N60">
-        <v>-65.96187520000001</v>
+        <v>-67.5577696</v>
       </c>
       <c r="O60">
-        <v>-8.245234400000001</v>
+        <v>-8.4447212</v>
       </c>
       <c r="P60">
-        <v>-57.71664080000001</v>
+        <v>-59.1130484</v>
       </c>
       <c r="Q60">
-        <v>-9.116640800000006</v>
+        <v>-10.5130484</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1818831301266651</v>
+        <v>0.1852022308614618</v>
       </c>
       <c r="T60">
-        <v>2.294557073900919</v>
+        <v>2.35052188058143</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0359219170183795</v>
+        <v>0.03531307096722053</v>
       </c>
       <c r="W60">
-        <v>0.2273296119670661</v>
+        <v>0.2274731778659294</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2873753361470361</v>
+        <v>0.2825045677377643</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6479,22 +6479,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2101420895940977</v>
+        <v>0.2120420895940977</v>
       </c>
       <c r="C61">
-        <v>-102.7162612207715</v>
+        <v>-111.901470392418</v>
       </c>
       <c r="D61">
-        <v>211.4957387792286</v>
+        <v>209.0785296075821</v>
       </c>
       <c r="E61">
-        <v>355.112</v>
+        <v>361.8800000000001</v>
       </c>
       <c r="F61">
-        <v>399.312</v>
+        <v>406.08</v>
       </c>
       <c r="G61">
         <v>85.09999999999999</v>
@@ -6515,37 +6515,37 @@
         <v>26.6</v>
       </c>
       <c r="M61">
-        <v>94.15776960000001</v>
+        <v>95.75366400000001</v>
       </c>
       <c r="N61">
-        <v>-67.5577696</v>
+        <v>-69.15366400000002</v>
       </c>
       <c r="O61">
-        <v>-8.4447212</v>
+        <v>-8.644208000000003</v>
       </c>
       <c r="P61">
-        <v>-59.1130484</v>
+        <v>-60.50945600000001</v>
       </c>
       <c r="Q61">
-        <v>-10.5130484</v>
+        <v>-11.90945600000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1852022308614618</v>
+        <v>0.1886872866329984</v>
       </c>
       <c r="T61">
-        <v>2.35052188058143</v>
+        <v>2.409284927595965</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03531307096722053</v>
+        <v>0.03472451978443352</v>
       </c>
       <c r="W61">
-        <v>0.2274731778659294</v>
+        <v>0.2276119582348306</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2825045677377643</v>
+        <v>0.2777961582754681</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6561,22 +6561,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2120420895940977</v>
+        <v>0.2139420895940977</v>
       </c>
       <c r="C62">
-        <v>-111.901470392418</v>
+        <v>-121.0320507981533</v>
       </c>
       <c r="D62">
-        <v>209.0785296075821</v>
+        <v>206.7159492018467</v>
       </c>
       <c r="E62">
-        <v>361.8800000000001</v>
+        <v>368.648</v>
       </c>
       <c r="F62">
-        <v>406.08</v>
+        <v>412.848</v>
       </c>
       <c r="G62">
         <v>85.09999999999999</v>
@@ -6597,37 +6597,37 @@
         <v>26.6</v>
       </c>
       <c r="M62">
-        <v>95.75366400000001</v>
+        <v>97.34955840000001</v>
       </c>
       <c r="N62">
-        <v>-69.15366400000002</v>
+        <v>-70.74955840000001</v>
       </c>
       <c r="O62">
-        <v>-8.644208000000003</v>
+        <v>-8.843694800000002</v>
       </c>
       <c r="P62">
-        <v>-60.50945600000001</v>
+        <v>-61.90586360000001</v>
       </c>
       <c r="Q62">
-        <v>-11.90945600000001</v>
+        <v>-13.30586360000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1886872866329984</v>
+        <v>0.1923510632133317</v>
       </c>
       <c r="T62">
-        <v>2.409284927595965</v>
+        <v>2.47106146420099</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03472451978443352</v>
+        <v>0.03415526536173789</v>
       </c>
       <c r="W62">
-        <v>0.2276119582348306</v>
+        <v>0.2277461884277022</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2777961582754681</v>
+        <v>0.273242122893903</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6643,22 +6643,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2139420895940977</v>
+        <v>0.2158420895940977</v>
       </c>
       <c r="C63">
-        <v>-121.0320507981533</v>
+        <v>-130.1098336549804</v>
       </c>
       <c r="D63">
-        <v>206.7159492018467</v>
+        <v>204.4061663450196</v>
       </c>
       <c r="E63">
-        <v>368.648</v>
+        <v>375.4160000000001</v>
       </c>
       <c r="F63">
-        <v>412.848</v>
+        <v>419.616</v>
       </c>
       <c r="G63">
         <v>85.09999999999999</v>
@@ -6679,37 +6679,37 @@
         <v>26.6</v>
       </c>
       <c r="M63">
-        <v>97.34955840000001</v>
+        <v>98.94545280000001</v>
       </c>
       <c r="N63">
-        <v>-70.74955840000001</v>
+        <v>-72.3454528</v>
       </c>
       <c r="O63">
-        <v>-8.843694800000002</v>
+        <v>-9.0431816</v>
       </c>
       <c r="P63">
-        <v>-61.90586360000001</v>
+        <v>-63.30227120000001</v>
       </c>
       <c r="Q63">
-        <v>-13.30586360000001</v>
+        <v>-14.70227120000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1923510632133317</v>
+        <v>0.1962076701399983</v>
       </c>
       <c r="T63">
-        <v>2.47106146420099</v>
+        <v>2.536089397469437</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03415526536173789</v>
+        <v>0.03360437398493567</v>
       </c>
       <c r="W63">
-        <v>0.2277461884277022</v>
+        <v>0.2278760886143522</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.273242122893903</v>
+        <v>0.2688349918794853</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6725,22 +6725,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2158420895940977</v>
+        <v>0.2177420895940977</v>
       </c>
       <c r="C64">
-        <v>-130.1098336549804</v>
+        <v>-139.1365692384107</v>
       </c>
       <c r="D64">
-        <v>204.4061663450196</v>
+        <v>202.1474307615894</v>
       </c>
       <c r="E64">
-        <v>375.4160000000001</v>
+        <v>382.1840000000001</v>
       </c>
       <c r="F64">
-        <v>419.616</v>
+        <v>426.3840000000001</v>
       </c>
       <c r="G64">
         <v>85.09999999999999</v>
@@ -6761,37 +6761,37 @@
         <v>26.6</v>
       </c>
       <c r="M64">
-        <v>98.94545280000001</v>
+        <v>100.5413472</v>
       </c>
       <c r="N64">
-        <v>-72.3454528</v>
+        <v>-73.94134720000002</v>
       </c>
       <c r="O64">
-        <v>-9.0431816</v>
+        <v>-9.242668400000003</v>
       </c>
       <c r="P64">
-        <v>-63.30227120000001</v>
+        <v>-64.69867880000002</v>
       </c>
       <c r="Q64">
-        <v>-14.70227120000001</v>
+        <v>-16.09867880000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1962076701399983</v>
+        <v>0.2002727423059442</v>
       </c>
       <c r="T64">
-        <v>2.536089397469437</v>
+        <v>2.6046323541578</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03360437398493567</v>
+        <v>0.03307097122327002</v>
       </c>
       <c r="W64">
-        <v>0.2278760886143522</v>
+        <v>0.2280018649855529</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2688349918794853</v>
+        <v>0.26456776978616</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6807,22 +6807,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2177420895940977</v>
+        <v>0.2196420895940977</v>
       </c>
       <c r="C65">
-        <v>-139.1365692384107</v>
+        <v>-148.1139313056971</v>
       </c>
       <c r="D65">
-        <v>202.1474307615894</v>
+        <v>199.9380686943029</v>
       </c>
       <c r="E65">
-        <v>382.1840000000001</v>
+        <v>388.9520000000001</v>
       </c>
       <c r="F65">
-        <v>426.3840000000001</v>
+        <v>433.152</v>
       </c>
       <c r="G65">
         <v>85.09999999999999</v>
@@ -6843,37 +6843,37 @@
         <v>26.6</v>
       </c>
       <c r="M65">
-        <v>100.5413472</v>
+        <v>102.1372416</v>
       </c>
       <c r="N65">
-        <v>-73.94134720000002</v>
+        <v>-75.53724160000002</v>
       </c>
       <c r="O65">
-        <v>-9.242668400000003</v>
+        <v>-9.442155200000002</v>
       </c>
       <c r="P65">
-        <v>-64.69867880000002</v>
+        <v>-66.09508640000001</v>
       </c>
       <c r="Q65">
-        <v>-16.09867880000002</v>
+        <v>-17.49508640000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2002727423059442</v>
+        <v>0.2045636518144427</v>
       </c>
       <c r="T65">
-        <v>2.6046323541578</v>
+        <v>2.676983252884406</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03307097122327002</v>
+        <v>0.03255423729790643</v>
       </c>
       <c r="W65">
-        <v>0.2280018649855529</v>
+        <v>0.2281237108451537</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.26456776978616</v>
+        <v>0.2604338983832514</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6889,22 +6889,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2196420895940977</v>
+        <v>0.2215420895940977</v>
       </c>
       <c r="C66">
-        <v>-148.1139313056971</v>
+        <v>-157.0435212321432</v>
       </c>
       <c r="D66">
-        <v>199.9380686943029</v>
+        <v>197.7764787678569</v>
       </c>
       <c r="E66">
-        <v>388.9520000000001</v>
+        <v>395.7200000000001</v>
       </c>
       <c r="F66">
-        <v>433.152</v>
+        <v>439.9200000000001</v>
       </c>
       <c r="G66">
         <v>85.09999999999999</v>
@@ -6925,37 +6925,37 @@
         <v>26.6</v>
       </c>
       <c r="M66">
-        <v>102.1372416</v>
+        <v>103.733136</v>
       </c>
       <c r="N66">
-        <v>-75.53724160000002</v>
+        <v>-77.13313600000001</v>
       </c>
       <c r="O66">
-        <v>-9.442155200000002</v>
+        <v>-9.641642000000001</v>
       </c>
       <c r="P66">
-        <v>-66.09508640000001</v>
+        <v>-67.491494</v>
       </c>
       <c r="Q66">
-        <v>-17.49508640000001</v>
+        <v>-18.891494</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2045636518144427</v>
+        <v>0.2090997561519982</v>
       </c>
       <c r="T66">
-        <v>2.676983252884406</v>
+        <v>2.753468488681104</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03255423729790643</v>
+        <v>0.03205340287793863</v>
       </c>
       <c r="W66">
-        <v>0.2281237108451537</v>
+        <v>0.2282418076013821</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2604338983832514</v>
+        <v>0.2564272230235092</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6971,22 +6971,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2215420895940977</v>
+        <v>0.2234420895940977</v>
       </c>
       <c r="C67">
-        <v>-157.0435212321432</v>
+        <v>-165.926871881967</v>
       </c>
       <c r="D67">
-        <v>197.7764787678569</v>
+        <v>195.6611281180331</v>
       </c>
       <c r="E67">
-        <v>395.7200000000001</v>
+        <v>402.4880000000001</v>
       </c>
       <c r="F67">
-        <v>439.9200000000001</v>
+        <v>446.688</v>
       </c>
       <c r="G67">
         <v>85.09999999999999</v>
@@ -7007,37 +7007,37 @@
         <v>26.6</v>
       </c>
       <c r="M67">
-        <v>103.733136</v>
+        <v>105.3290304</v>
       </c>
       <c r="N67">
-        <v>-77.13313600000001</v>
+        <v>-78.72903040000003</v>
       </c>
       <c r="O67">
-        <v>-9.641642000000001</v>
+        <v>-9.841128800000003</v>
       </c>
       <c r="P67">
-        <v>-67.491494</v>
+        <v>-68.88790160000002</v>
       </c>
       <c r="Q67">
-        <v>-18.891494</v>
+        <v>-20.28790160000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2090997561519982</v>
+        <v>0.2139026901564687</v>
       </c>
       <c r="T67">
-        <v>2.753468488681104</v>
+        <v>2.834452855995254</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03205340287793863</v>
+        <v>0.03156774525857593</v>
       </c>
       <c r="W67">
-        <v>0.2282418076013821</v>
+        <v>0.2283563256680278</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2564272230235092</v>
+        <v>0.2525419620686074</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7053,22 +7053,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2234420895940977</v>
+        <v>0.2253420895940977</v>
       </c>
       <c r="C68">
-        <v>-165.926871881967</v>
+        <v>-174.7654512333866</v>
       </c>
       <c r="D68">
-        <v>195.6611281180331</v>
+        <v>193.5905487666135</v>
       </c>
       <c r="E68">
-        <v>402.4880000000001</v>
+        <v>409.2560000000001</v>
       </c>
       <c r="F68">
-        <v>446.688</v>
+        <v>453.4560000000001</v>
       </c>
       <c r="G68">
         <v>85.09999999999999</v>
@@ -7089,37 +7089,37 @@
         <v>26.6</v>
       </c>
       <c r="M68">
-        <v>105.3290304</v>
+        <v>106.9249248</v>
       </c>
       <c r="N68">
-        <v>-78.72903040000003</v>
+        <v>-80.32492480000002</v>
       </c>
       <c r="O68">
-        <v>-9.841128800000003</v>
+        <v>-10.0406156</v>
       </c>
       <c r="P68">
-        <v>-68.88790160000002</v>
+        <v>-70.28430920000002</v>
       </c>
       <c r="Q68">
-        <v>-20.28790160000002</v>
+        <v>-21.68430920000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2139026901564687</v>
+        <v>0.2189967110703011</v>
       </c>
       <c r="T68">
-        <v>2.834452855995254</v>
+        <v>2.920345366782989</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03156774525857593</v>
+        <v>0.03109658488158225</v>
       </c>
       <c r="W68">
-        <v>0.2283563256680278</v>
+        <v>0.2284674252849229</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2525419620686074</v>
+        <v>0.2487726790526581</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7135,22 +7135,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2253420895940977</v>
+        <v>0.2272420895940977</v>
       </c>
       <c r="C69">
-        <v>-174.7654512333866</v>
+        <v>-183.5606657759407</v>
       </c>
       <c r="D69">
-        <v>193.5905487666135</v>
+        <v>191.5633342240594</v>
       </c>
       <c r="E69">
-        <v>409.2560000000001</v>
+        <v>416.0240000000001</v>
       </c>
       <c r="F69">
-        <v>453.4560000000001</v>
+        <v>460.2240000000001</v>
       </c>
       <c r="G69">
         <v>85.09999999999999</v>
@@ -7171,37 +7171,37 @@
         <v>26.6</v>
       </c>
       <c r="M69">
-        <v>106.9249248</v>
+        <v>108.5208192</v>
       </c>
       <c r="N69">
-        <v>-80.32492480000002</v>
+        <v>-81.92081920000004</v>
       </c>
       <c r="O69">
-        <v>-10.0406156</v>
+        <v>-10.2401024</v>
       </c>
       <c r="P69">
-        <v>-70.28430920000002</v>
+        <v>-71.68071680000003</v>
       </c>
       <c r="Q69">
-        <v>-21.68430920000002</v>
+        <v>-23.08071680000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2189967110703011</v>
+        <v>0.224409108291248</v>
       </c>
       <c r="T69">
-        <v>2.920345366782989</v>
+        <v>3.011606159494957</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03109658488158225</v>
+        <v>0.03063928216273545</v>
       </c>
       <c r="W69">
-        <v>0.2284674252849229</v>
+        <v>0.228575257266027</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2487726790526581</v>
+        <v>0.2451142573018835</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7217,22 +7217,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2272420895940977</v>
+        <v>0.2291420895940977</v>
       </c>
       <c r="C70">
-        <v>-183.5606657759407</v>
+        <v>-192.3138636965683</v>
       </c>
       <c r="D70">
-        <v>191.5633342240594</v>
+        <v>189.5781363034318</v>
       </c>
       <c r="E70">
-        <v>416.0240000000001</v>
+        <v>422.7920000000001</v>
       </c>
       <c r="F70">
-        <v>460.2240000000001</v>
+        <v>466.9920000000001</v>
       </c>
       <c r="G70">
         <v>85.09999999999999</v>
@@ -7253,37 +7253,37 @@
         <v>26.6</v>
       </c>
       <c r="M70">
-        <v>108.5208192</v>
+        <v>110.1167136</v>
       </c>
       <c r="N70">
-        <v>-81.92081920000004</v>
+        <v>-83.51671360000003</v>
       </c>
       <c r="O70">
-        <v>-10.2401024</v>
+        <v>-10.4395892</v>
       </c>
       <c r="P70">
-        <v>-71.68071680000003</v>
+        <v>-73.07712440000003</v>
       </c>
       <c r="Q70">
-        <v>-23.08071680000003</v>
+        <v>-24.47712440000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.224409108291248</v>
+        <v>0.2301706924296754</v>
       </c>
       <c r="T70">
-        <v>3.011606159494957</v>
+        <v>3.108754745285117</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03063928216273545</v>
+        <v>0.03019523459515958</v>
       </c>
       <c r="W70">
-        <v>0.228575257266027</v>
+        <v>0.2286799636824614</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2451142573018835</v>
+        <v>0.2415618767612766</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7299,22 +7299,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2291420895940977</v>
+        <v>0.2310420895940977</v>
       </c>
       <c r="C71">
-        <v>-192.3138636965683</v>
+        <v>-201.0263378696129</v>
       </c>
       <c r="D71">
-        <v>189.5781363034318</v>
+        <v>187.6336621303873</v>
       </c>
       <c r="E71">
-        <v>422.7920000000001</v>
+        <v>429.5600000000001</v>
       </c>
       <c r="F71">
-        <v>466.9920000000001</v>
+        <v>473.7600000000001</v>
       </c>
       <c r="G71">
         <v>85.09999999999999</v>
@@ -7335,37 +7335,37 @@
         <v>26.6</v>
       </c>
       <c r="M71">
-        <v>110.1167136</v>
+        <v>111.712608</v>
       </c>
       <c r="N71">
-        <v>-83.51671360000003</v>
+        <v>-85.11260800000002</v>
       </c>
       <c r="O71">
-        <v>-10.4395892</v>
+        <v>-10.639076</v>
       </c>
       <c r="P71">
-        <v>-73.07712440000003</v>
+        <v>-74.47353200000002</v>
       </c>
       <c r="Q71">
-        <v>-24.47712440000003</v>
+        <v>-25.87353200000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2301706924296754</v>
+        <v>0.2363163821773312</v>
       </c>
       <c r="T71">
-        <v>3.108754745285117</v>
+        <v>3.212379903461288</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03019523459515958</v>
+        <v>0.02976387410094301</v>
       </c>
       <c r="W71">
-        <v>0.2286799636824614</v>
+        <v>0.2287816784869976</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2415618767612766</v>
+        <v>0.2381109928075442</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7381,22 +7381,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2310420895940977</v>
+        <v>0.2329420895940977</v>
       </c>
       <c r="C72">
-        <v>-201.0263378696129</v>
+        <v>-209.6993286646872</v>
       </c>
       <c r="D72">
-        <v>187.6336621303873</v>
+        <v>185.7286713353129</v>
       </c>
       <c r="E72">
-        <v>429.5600000000001</v>
+        <v>436.3280000000001</v>
       </c>
       <c r="F72">
-        <v>473.7600000000001</v>
+        <v>480.5280000000001</v>
       </c>
       <c r="G72">
         <v>85.09999999999999</v>
@@ -7417,37 +7417,37 @@
         <v>26.6</v>
       </c>
       <c r="M72">
-        <v>111.712608</v>
+        <v>113.3085024</v>
       </c>
       <c r="N72">
-        <v>-85.11260800000002</v>
+        <v>-86.70850240000001</v>
       </c>
       <c r="O72">
-        <v>-10.639076</v>
+        <v>-10.8385628</v>
       </c>
       <c r="P72">
-        <v>-74.47353200000002</v>
+        <v>-75.86993960000001</v>
       </c>
       <c r="Q72">
-        <v>-25.87353200000002</v>
+        <v>-27.26993960000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2363163821773312</v>
+        <v>0.2428859125972392</v>
       </c>
       <c r="T72">
-        <v>3.212379903461288</v>
+        <v>3.323151624270298</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02976387410094301</v>
+        <v>0.02934466460656353</v>
       </c>
       <c r="W72">
-        <v>0.2287816784869976</v>
+        <v>0.2288805280857723</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2381109928075442</v>
+        <v>0.2347573168525083</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7463,22 +7463,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2329420895940977</v>
+        <v>0.2348420895940977</v>
       </c>
       <c r="C73">
-        <v>-209.6993286646871</v>
+        <v>-218.3340265852126</v>
       </c>
       <c r="D73">
-        <v>185.7286713353129</v>
+        <v>183.8619734147875</v>
       </c>
       <c r="E73">
-        <v>436.328</v>
+        <v>443.0960000000001</v>
       </c>
       <c r="F73">
-        <v>480.528</v>
+        <v>487.296</v>
       </c>
       <c r="G73">
         <v>85.09999999999999</v>
@@ -7499,37 +7499,37 @@
         <v>26.6</v>
       </c>
       <c r="M73">
-        <v>113.3085024</v>
+        <v>114.9043968</v>
       </c>
       <c r="N73">
-        <v>-86.70850240000001</v>
+        <v>-88.30439680000001</v>
       </c>
       <c r="O73">
-        <v>-10.8385628</v>
+        <v>-11.0380496</v>
       </c>
       <c r="P73">
-        <v>-75.86993960000001</v>
+        <v>-77.26634720000001</v>
       </c>
       <c r="Q73">
-        <v>-27.26993960000001</v>
+        <v>-28.66634720000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2428859125972392</v>
+        <v>0.2499246951899977</v>
       </c>
       <c r="T73">
-        <v>3.323151624270297</v>
+        <v>3.441835610851379</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02934466460656354</v>
+        <v>0.02893709982036127</v>
       </c>
       <c r="W73">
-        <v>0.2288805280857723</v>
+        <v>0.2289766318623588</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2347573168525082</v>
+        <v>0.2314967985628902</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7545,22 +7545,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2348420895940977</v>
+        <v>0.2367420895940977</v>
       </c>
       <c r="C74">
-        <v>-218.3340265852126</v>
+        <v>-226.9315747494267</v>
       </c>
       <c r="D74">
-        <v>183.8619734147875</v>
+        <v>182.0324252505733</v>
       </c>
       <c r="E74">
-        <v>443.0960000000001</v>
+        <v>449.864</v>
       </c>
       <c r="F74">
-        <v>487.296</v>
+        <v>494.064</v>
       </c>
       <c r="G74">
         <v>85.09999999999999</v>
@@ -7581,37 +7581,37 @@
         <v>26.6</v>
       </c>
       <c r="M74">
-        <v>114.9043968</v>
+        <v>116.5002912</v>
       </c>
       <c r="N74">
-        <v>-88.30439680000001</v>
+        <v>-89.9002912</v>
       </c>
       <c r="O74">
-        <v>-11.0380496</v>
+        <v>-11.2375364</v>
       </c>
       <c r="P74">
-        <v>-77.26634720000001</v>
+        <v>-78.6627548</v>
       </c>
       <c r="Q74">
-        <v>-28.66634720000001</v>
+        <v>-30.0627548</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2499246951899977</v>
+        <v>0.2574848690859236</v>
       </c>
       <c r="T74">
-        <v>3.441835610851379</v>
+        <v>3.569311003845875</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02893709982036127</v>
+        <v>0.02854070119268509</v>
       </c>
       <c r="W74">
-        <v>0.2289766318623588</v>
+        <v>0.2290701026587649</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2314967985628902</v>
+        <v>0.2283256095414807</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7627,22 +7627,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2367420895940977</v>
+        <v>0.2386420895940977</v>
       </c>
       <c r="C75">
-        <v>-226.9315747494267</v>
+        <v>-235.4930712247246</v>
       </c>
       <c r="D75">
-        <v>182.0324252505733</v>
+        <v>180.2389287752754</v>
       </c>
       <c r="E75">
-        <v>449.864</v>
+        <v>456.6320000000001</v>
       </c>
       <c r="F75">
-        <v>494.064</v>
+        <v>500.8320000000001</v>
       </c>
       <c r="G75">
         <v>85.09999999999999</v>
@@ -7663,37 +7663,37 @@
         <v>26.6</v>
       </c>
       <c r="M75">
-        <v>116.5002912</v>
+        <v>118.0961856</v>
       </c>
       <c r="N75">
-        <v>-89.9002912</v>
+        <v>-91.49618560000002</v>
       </c>
       <c r="O75">
-        <v>-11.2375364</v>
+        <v>-11.4370232</v>
       </c>
       <c r="P75">
-        <v>-78.6627548</v>
+        <v>-80.05916240000002</v>
       </c>
       <c r="Q75">
-        <v>-30.0627548</v>
+        <v>-31.45916240000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2574848690859236</v>
+        <v>0.2656265948199975</v>
       </c>
       <c r="T75">
-        <v>3.569311003845875</v>
+        <v>3.706592196301485</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02854070119268509</v>
+        <v>0.02815501604143258</v>
       </c>
       <c r="W75">
-        <v>0.2290701026587649</v>
+        <v>0.2291610472174302</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2283256095414807</v>
+        <v>0.2252401283314606</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7709,22 +7709,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2386420895940977</v>
+        <v>0.2405420895940977</v>
       </c>
       <c r="C76">
-        <v>-235.4930712247246</v>
+        <v>-244.0195712253501</v>
       </c>
       <c r="D76">
-        <v>180.2389287752754</v>
+        <v>178.48042877465</v>
       </c>
       <c r="E76">
-        <v>456.6320000000001</v>
+        <v>463.4</v>
       </c>
       <c r="F76">
-        <v>500.8320000000001</v>
+        <v>507.6</v>
       </c>
       <c r="G76">
         <v>85.09999999999999</v>
@@ -7745,37 +7745,37 @@
         <v>26.6</v>
       </c>
       <c r="M76">
-        <v>118.0961856</v>
+        <v>119.69208</v>
       </c>
       <c r="N76">
-        <v>-91.49618560000002</v>
+        <v>-93.09208000000001</v>
       </c>
       <c r="O76">
-        <v>-11.4370232</v>
+        <v>-11.63651</v>
       </c>
       <c r="P76">
-        <v>-80.05916240000002</v>
+        <v>-81.45557000000001</v>
       </c>
       <c r="Q76">
-        <v>-31.45916240000002</v>
+        <v>-32.85557000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2656265948199975</v>
+        <v>0.2744196586127974</v>
       </c>
       <c r="T76">
-        <v>3.706592196301485</v>
+        <v>3.854855884153545</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02815501604143258</v>
+        <v>0.02777961582754682</v>
       </c>
       <c r="W76">
-        <v>0.2291610472174302</v>
+        <v>0.2292495665878645</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2252401283314606</v>
+        <v>0.2222369266203745</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7791,22 +7791,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2405420895940977</v>
+        <v>0.2424420895940977</v>
       </c>
       <c r="C77">
-        <v>-244.0195712253501</v>
+        <v>-252.5120891826796</v>
       </c>
       <c r="D77">
-        <v>178.48042877465</v>
+        <v>176.7559108173205</v>
       </c>
       <c r="E77">
-        <v>463.4</v>
+        <v>470.1680000000001</v>
       </c>
       <c r="F77">
-        <v>507.6</v>
+        <v>514.3680000000001</v>
       </c>
       <c r="G77">
         <v>85.09999999999999</v>
@@ -7827,37 +7827,37 @@
         <v>26.6</v>
       </c>
       <c r="M77">
-        <v>119.69208</v>
+        <v>121.2879744</v>
       </c>
       <c r="N77">
-        <v>-93.09208000000001</v>
+        <v>-94.6879744</v>
       </c>
       <c r="O77">
-        <v>-11.63651</v>
+        <v>-11.8359968</v>
       </c>
       <c r="P77">
-        <v>-81.45557000000001</v>
+        <v>-82.8519776</v>
       </c>
       <c r="Q77">
-        <v>-32.85557000000001</v>
+        <v>-34.2519776</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2744196586127974</v>
+        <v>0.283945477721664</v>
       </c>
       <c r="T77">
-        <v>3.854855884153545</v>
+        <v>4.01547487932661</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02777961582754682</v>
+        <v>0.02741409456665804</v>
       </c>
       <c r="W77">
-        <v>0.2292495665878645</v>
+        <v>0.229335756501182</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2222369266203745</v>
+        <v>0.2193127565332644</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7873,22 +7873,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2424420895940977</v>
+        <v>0.2443420895940977</v>
       </c>
       <c r="C78">
-        <v>-252.5120891826796</v>
+        <v>-260.9716006966337</v>
       </c>
       <c r="D78">
-        <v>176.7559108173205</v>
+        <v>175.0643993033664</v>
       </c>
       <c r="E78">
-        <v>470.1680000000001</v>
+        <v>476.9360000000001</v>
       </c>
       <c r="F78">
-        <v>514.3680000000001</v>
+        <v>521.1360000000001</v>
       </c>
       <c r="G78">
         <v>85.09999999999999</v>
@@ -7909,37 +7909,37 @@
         <v>26.6</v>
       </c>
       <c r="M78">
-        <v>121.2879744</v>
+        <v>122.8838688</v>
       </c>
       <c r="N78">
-        <v>-94.6879744</v>
+        <v>-96.28386880000002</v>
       </c>
       <c r="O78">
-        <v>-11.8359968</v>
+        <v>-12.0354836</v>
       </c>
       <c r="P78">
-        <v>-82.8519776</v>
+        <v>-84.24838520000002</v>
       </c>
       <c r="Q78">
-        <v>-34.2519776</v>
+        <v>-35.64838520000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.283945477721664</v>
+        <v>0.2942996289269537</v>
       </c>
       <c r="T78">
-        <v>4.01547487932661</v>
+        <v>4.190060743645157</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02741409456665804</v>
+        <v>0.02705806736449365</v>
       </c>
       <c r="W78">
-        <v>0.229335756501182</v>
+        <v>0.2294197077154524</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2193127565332644</v>
+        <v>0.2164645389159493</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7955,22 +7955,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2443420895940977</v>
+        <v>0.2462420895940977</v>
       </c>
       <c r="C79">
-        <v>-260.9716006966337</v>
+        <v>-269.3990443761023</v>
       </c>
       <c r="D79">
-        <v>175.0643993033664</v>
+        <v>173.4049556238978</v>
       </c>
       <c r="E79">
-        <v>476.9360000000001</v>
+        <v>483.7040000000001</v>
       </c>
       <c r="F79">
-        <v>521.1360000000001</v>
+        <v>527.9040000000001</v>
       </c>
       <c r="G79">
         <v>85.09999999999999</v>
@@ -7991,37 +7991,37 @@
         <v>26.6</v>
       </c>
       <c r="M79">
-        <v>122.8838688</v>
+        <v>124.4797632</v>
       </c>
       <c r="N79">
-        <v>-96.28386880000002</v>
+        <v>-97.87976320000004</v>
       </c>
       <c r="O79">
-        <v>-12.0354836</v>
+        <v>-12.23497040000001</v>
       </c>
       <c r="P79">
-        <v>-84.24838520000002</v>
+        <v>-85.64479280000003</v>
       </c>
       <c r="Q79">
-        <v>-35.64838520000001</v>
+        <v>-37.04479280000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2942996289269537</v>
+        <v>0.3055950666054517</v>
       </c>
       <c r="T79">
-        <v>4.190060743645157</v>
+        <v>4.380518050174484</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02705806736449365</v>
+        <v>0.02671116906494886</v>
       </c>
       <c r="W79">
-        <v>0.2294197077154524</v>
+        <v>0.2295015063344851</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2164645389159493</v>
+        <v>0.2136893525195908</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8037,22 +8037,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2462420895940977</v>
+        <v>0.2481420895940977</v>
       </c>
       <c r="C80">
-        <v>-269.3990443761023</v>
+        <v>-277.7953235756812</v>
       </c>
       <c r="D80">
-        <v>173.4049556238978</v>
+        <v>171.7766764243189</v>
       </c>
       <c r="E80">
-        <v>483.7040000000001</v>
+        <v>490.472</v>
       </c>
       <c r="F80">
-        <v>527.9040000000001</v>
+        <v>534.672</v>
       </c>
       <c r="G80">
         <v>85.09999999999999</v>
@@ -8073,37 +8073,37 @@
         <v>26.6</v>
       </c>
       <c r="M80">
-        <v>124.4797632</v>
+        <v>126.0756576</v>
       </c>
       <c r="N80">
-        <v>-97.87976320000004</v>
+        <v>-99.47565760000001</v>
       </c>
       <c r="O80">
-        <v>-12.23497040000001</v>
+        <v>-12.4344572</v>
       </c>
       <c r="P80">
-        <v>-85.64479280000003</v>
+        <v>-87.04120040000001</v>
       </c>
       <c r="Q80">
-        <v>-37.04479280000003</v>
+        <v>-38.44120040000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3055950666054517</v>
+        <v>0.3179662602533304</v>
       </c>
       <c r="T80">
-        <v>4.380518050174484</v>
+        <v>4.58911414780184</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02671116906494886</v>
+        <v>0.02637305300083559</v>
       </c>
       <c r="W80">
-        <v>0.2295015063344851</v>
+        <v>0.229581234102403</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2136893525195908</v>
+        <v>0.2109844240066847</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8119,22 +8119,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2481420895940977</v>
+        <v>0.2500420895940977</v>
       </c>
       <c r="C81">
-        <v>-277.7953235756812</v>
+        <v>-286.1613080354703</v>
       </c>
       <c r="D81">
-        <v>171.7766764243189</v>
+        <v>170.1786919645298</v>
       </c>
       <c r="E81">
-        <v>490.472</v>
+        <v>497.2400000000001</v>
       </c>
       <c r="F81">
-        <v>534.672</v>
+        <v>541.4400000000001</v>
       </c>
       <c r="G81">
         <v>85.09999999999999</v>
@@ -8155,37 +8155,37 @@
         <v>26.6</v>
       </c>
       <c r="M81">
-        <v>126.0756576</v>
+        <v>127.671552</v>
       </c>
       <c r="N81">
-        <v>-99.47565760000001</v>
+        <v>-101.071552</v>
       </c>
       <c r="O81">
-        <v>-12.4344572</v>
+        <v>-12.633944</v>
       </c>
       <c r="P81">
-        <v>-87.04120040000001</v>
+        <v>-88.43760800000003</v>
       </c>
       <c r="Q81">
-        <v>-38.44120040000001</v>
+        <v>-39.83760800000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3179662602533304</v>
+        <v>0.3315745732659969</v>
       </c>
       <c r="T81">
-        <v>4.58911414780184</v>
+        <v>4.818569855191932</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02637305300083559</v>
+        <v>0.02604338983832514</v>
       </c>
       <c r="W81">
-        <v>0.229581234102403</v>
+        <v>0.229658968676123</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2109844240066847</v>
+        <v>0.2083471187066011</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8201,22 +8201,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2500420895940977</v>
+        <v>0.2519420895940977</v>
       </c>
       <c r="C82">
-        <v>-286.1613080354703</v>
+        <v>-294.4978354301875</v>
       </c>
       <c r="D82">
-        <v>170.1786919645298</v>
+        <v>168.6101645698126</v>
       </c>
       <c r="E82">
-        <v>497.2400000000001</v>
+        <v>504.0080000000001</v>
       </c>
       <c r="F82">
-        <v>541.4400000000001</v>
+        <v>548.2080000000001</v>
       </c>
       <c r="G82">
         <v>85.09999999999999</v>
@@ -8237,37 +8237,37 @@
         <v>26.6</v>
       </c>
       <c r="M82">
-        <v>127.671552</v>
+        <v>129.2674464</v>
       </c>
       <c r="N82">
-        <v>-101.071552</v>
+        <v>-102.6674464</v>
       </c>
       <c r="O82">
-        <v>-12.633944</v>
+        <v>-12.8334308</v>
       </c>
       <c r="P82">
-        <v>-88.43760800000003</v>
+        <v>-89.83401560000001</v>
       </c>
       <c r="Q82">
-        <v>-39.83760800000002</v>
+        <v>-41.23401560000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3315745732659969</v>
+        <v>0.3466153402799967</v>
       </c>
       <c r="T82">
-        <v>4.818569855191932</v>
+        <v>5.072178794938876</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02604338983832514</v>
+        <v>0.02572186650698779</v>
       </c>
       <c r="W82">
-        <v>0.229658968676123</v>
+        <v>0.2297347838776523</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2083471187066011</v>
+        <v>0.2057749320559022</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8283,22 +8283,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2519420895940977</v>
+        <v>0.2538420895940977</v>
       </c>
       <c r="C83">
-        <v>-294.4978354301875</v>
+        <v>-302.805712833398</v>
       </c>
       <c r="D83">
-        <v>168.6101645698126</v>
+        <v>167.070287166602</v>
       </c>
       <c r="E83">
-        <v>504.0080000000001</v>
+        <v>510.7760000000001</v>
       </c>
       <c r="F83">
-        <v>548.2080000000001</v>
+        <v>554.9760000000001</v>
       </c>
       <c r="G83">
         <v>85.09999999999999</v>
@@ -8319,37 +8319,37 @@
         <v>26.6</v>
       </c>
       <c r="M83">
-        <v>129.2674464</v>
+        <v>130.8633408</v>
       </c>
       <c r="N83">
-        <v>-102.6674464</v>
+        <v>-104.2633408</v>
       </c>
       <c r="O83">
-        <v>-12.8334308</v>
+        <v>-13.0329176</v>
       </c>
       <c r="P83">
-        <v>-89.83401560000001</v>
+        <v>-91.23042320000003</v>
       </c>
       <c r="Q83">
-        <v>-41.23401560000001</v>
+        <v>-42.63042320000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3466153402799967</v>
+        <v>0.3633273036288854</v>
       </c>
       <c r="T83">
-        <v>5.072178794938876</v>
+        <v>5.353966505768814</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02572186650698779</v>
+        <v>0.02540818520812209</v>
       </c>
       <c r="W83">
-        <v>0.2297347838776523</v>
+        <v>0.2298087499279248</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2057749320559022</v>
+        <v>0.2032654816649766</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8365,22 +8365,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2538420895940977</v>
+        <v>0.2557420895940977</v>
       </c>
       <c r="C84">
-        <v>-302.805712833398</v>
+        <v>-311.0857181022333</v>
       </c>
       <c r="D84">
-        <v>167.070287166602</v>
+        <v>165.5582818977668</v>
       </c>
       <c r="E84">
-        <v>510.7760000000001</v>
+        <v>517.5440000000001</v>
       </c>
       <c r="F84">
-        <v>554.9760000000001</v>
+        <v>561.7440000000001</v>
       </c>
       <c r="G84">
         <v>85.09999999999999</v>
@@ -8401,37 +8401,37 @@
         <v>26.6</v>
       </c>
       <c r="M84">
-        <v>130.8633408</v>
+        <v>132.4592352000001</v>
       </c>
       <c r="N84">
-        <v>-104.2633408</v>
+        <v>-105.8592352000001</v>
       </c>
       <c r="O84">
-        <v>-13.0329176</v>
+        <v>-13.23240440000001</v>
       </c>
       <c r="P84">
-        <v>-91.23042320000003</v>
+        <v>-92.62683080000005</v>
       </c>
       <c r="Q84">
-        <v>-42.63042320000003</v>
+        <v>-44.02683080000005</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3633273036288854</v>
+        <v>0.3820053803129375</v>
       </c>
       <c r="T84">
-        <v>5.353966505768814</v>
+        <v>5.668905711990509</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02540818520812209</v>
+        <v>0.02510206249477121</v>
       </c>
       <c r="W84">
-        <v>0.2298087499279248</v>
+        <v>0.229880933663733</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2032654816649766</v>
+        <v>0.2008164999581696</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8447,22 +8447,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2557420895940977</v>
+        <v>0.2576420895940977</v>
       </c>
       <c r="C85">
-        <v>-311.0857181022333</v>
+        <v>-319.338601187594</v>
       </c>
       <c r="D85">
-        <v>165.5582818977668</v>
+        <v>164.0733988124061</v>
       </c>
       <c r="E85">
-        <v>517.5440000000001</v>
+        <v>524.312</v>
       </c>
       <c r="F85">
-        <v>561.7440000000001</v>
+        <v>568.5120000000001</v>
       </c>
       <c r="G85">
         <v>85.09999999999999</v>
@@ -8483,37 +8483,37 @@
         <v>26.6</v>
       </c>
       <c r="M85">
-        <v>132.4592352000001</v>
+        <v>134.0551296</v>
       </c>
       <c r="N85">
-        <v>-105.8592352000001</v>
+        <v>-107.4551296</v>
       </c>
       <c r="O85">
-        <v>-13.23240440000001</v>
+        <v>-13.4318912</v>
       </c>
       <c r="P85">
-        <v>-92.62683080000005</v>
+        <v>-94.02323840000003</v>
       </c>
       <c r="Q85">
-        <v>-44.02683080000005</v>
+        <v>-45.42323840000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3820053803129375</v>
+        <v>0.4030182165824962</v>
       </c>
       <c r="T85">
-        <v>5.668905711990509</v>
+        <v>6.023212318989917</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02510206249477121</v>
+        <v>0.02480322841745251</v>
       </c>
       <c r="W85">
-        <v>0.229880933663733</v>
+        <v>0.2299513987391647</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2008164999581696</v>
+        <v>0.1984258273396201</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8529,22 +8529,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2576420895940977</v>
+        <v>0.2595420895940977</v>
       </c>
       <c r="C86">
-        <v>-319.338601187594</v>
+        <v>-327.5650853744734</v>
       </c>
       <c r="D86">
-        <v>164.0733988124061</v>
+        <v>162.6149146255267</v>
       </c>
       <c r="E86">
-        <v>524.312</v>
+        <v>531.08</v>
       </c>
       <c r="F86">
-        <v>568.5120000000001</v>
+        <v>575.2800000000001</v>
       </c>
       <c r="G86">
         <v>85.09999999999999</v>
@@ -8565,37 +8565,37 @@
         <v>26.6</v>
       </c>
       <c r="M86">
-        <v>134.0551296</v>
+        <v>135.651024</v>
       </c>
       <c r="N86">
-        <v>-107.4551296</v>
+        <v>-109.051024</v>
       </c>
       <c r="O86">
-        <v>-13.4318912</v>
+        <v>-13.63137800000001</v>
       </c>
       <c r="P86">
-        <v>-94.02323840000003</v>
+        <v>-95.41964600000003</v>
       </c>
       <c r="Q86">
-        <v>-45.42323840000002</v>
+        <v>-46.81964600000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4030182165824959</v>
+        <v>0.4268327643546623</v>
       </c>
       <c r="T86">
-        <v>6.023212318989913</v>
+        <v>6.424759806922574</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02480322841745251</v>
+        <v>0.02451142573018836</v>
       </c>
       <c r="W86">
-        <v>0.2299513987391647</v>
+        <v>0.2300202058128216</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1984258273396201</v>
+        <v>0.1960914058415069</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8611,22 +8611,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2595420895940977</v>
+        <v>0.2614420895940976</v>
       </c>
       <c r="C87">
-        <v>-327.5650853744734</v>
+        <v>-335.7658684567096</v>
       </c>
       <c r="D87">
-        <v>162.6149146255267</v>
+        <v>161.1821315432904</v>
       </c>
       <c r="E87">
-        <v>531.08</v>
+        <v>537.848</v>
       </c>
       <c r="F87">
-        <v>575.2800000000001</v>
+        <v>582.048</v>
       </c>
       <c r="G87">
         <v>85.09999999999999</v>
@@ -8647,37 +8647,37 @@
         <v>26.6</v>
       </c>
       <c r="M87">
-        <v>135.651024</v>
+        <v>137.2469184</v>
       </c>
       <c r="N87">
-        <v>-109.051024</v>
+        <v>-110.6469184</v>
       </c>
       <c r="O87">
-        <v>-13.63137800000001</v>
+        <v>-13.8308648</v>
       </c>
       <c r="P87">
-        <v>-95.41964600000003</v>
+        <v>-96.8160536</v>
       </c>
       <c r="Q87">
-        <v>-46.81964600000003</v>
+        <v>-48.2160536</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4268327643546623</v>
+        <v>0.4540493903799954</v>
       </c>
       <c r="T87">
-        <v>6.424759806922574</v>
+        <v>6.883671221702758</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02451142573018836</v>
+        <v>0.02422640915193036</v>
       </c>
       <c r="W87">
-        <v>0.2300202058128216</v>
+        <v>0.2300874127219748</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1960914058415069</v>
+        <v>0.1938112732154429</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8693,22 +8693,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2614420895940976</v>
+        <v>0.2633420895940977</v>
       </c>
       <c r="C88">
-        <v>-335.7658684567096</v>
+        <v>-343.9416238501771</v>
       </c>
       <c r="D88">
-        <v>161.1821315432904</v>
+        <v>159.774376149823</v>
       </c>
       <c r="E88">
-        <v>537.848</v>
+        <v>544.616</v>
       </c>
       <c r="F88">
-        <v>582.048</v>
+        <v>588.816</v>
       </c>
       <c r="G88">
         <v>85.09999999999999</v>
@@ -8729,37 +8729,37 @@
         <v>26.6</v>
       </c>
       <c r="M88">
-        <v>137.2469184</v>
+        <v>138.8428128</v>
       </c>
       <c r="N88">
-        <v>-110.6469184</v>
+        <v>-112.2428128</v>
       </c>
       <c r="O88">
-        <v>-13.8308648</v>
+        <v>-14.0303516</v>
       </c>
       <c r="P88">
-        <v>-96.8160536</v>
+        <v>-98.21246120000002</v>
       </c>
       <c r="Q88">
-        <v>-48.2160536</v>
+        <v>-49.61246120000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4540493903799954</v>
+        <v>0.485453189639995</v>
       </c>
       <c r="T88">
-        <v>6.883671221702758</v>
+        <v>7.41318439260297</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02422640915193036</v>
+        <v>0.02394794467891967</v>
       </c>
       <c r="W88">
-        <v>0.2300874127219748</v>
+        <v>0.2301530746447107</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1938112732154429</v>
+        <v>0.1915835574313574</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8775,22 +8775,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2633420895940977</v>
+        <v>0.2652420895940977</v>
       </c>
       <c r="C89">
-        <v>-343.9416238501771</v>
+        <v>-352.0930016481473</v>
       </c>
       <c r="D89">
-        <v>159.774376149823</v>
+        <v>158.3909983518528</v>
       </c>
       <c r="E89">
-        <v>544.616</v>
+        <v>551.384</v>
       </c>
       <c r="F89">
-        <v>588.816</v>
+        <v>595.5840000000001</v>
       </c>
       <c r="G89">
         <v>85.09999999999999</v>
@@ -8811,37 +8811,37 @@
         <v>26.6</v>
       </c>
       <c r="M89">
-        <v>138.8428128</v>
+        <v>140.4387072</v>
       </c>
       <c r="N89">
-        <v>-112.2428128</v>
+        <v>-113.8387072</v>
       </c>
       <c r="O89">
-        <v>-14.0303516</v>
+        <v>-14.2298384</v>
       </c>
       <c r="P89">
-        <v>-98.21246120000002</v>
+        <v>-99.60886880000001</v>
       </c>
       <c r="Q89">
-        <v>-49.61246120000002</v>
+        <v>-51.00886880000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.485453189639995</v>
+        <v>0.5220909554433281</v>
       </c>
       <c r="T89">
-        <v>7.41318439260297</v>
+        <v>8.03094975865322</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02394794467891967</v>
+        <v>0.02367580894393195</v>
       </c>
       <c r="W89">
-        <v>0.2301530746447107</v>
+        <v>0.2302172442510209</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1915835574313574</v>
+        <v>0.1894064715514555</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8857,22 +8857,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2652420895940977</v>
+        <v>0.2671420895940977</v>
       </c>
       <c r="C90">
-        <v>-352.0930016481473</v>
+        <v>-360.2206296222954</v>
       </c>
       <c r="D90">
-        <v>158.3909983518528</v>
+        <v>157.0313703777047</v>
       </c>
       <c r="E90">
-        <v>551.384</v>
+        <v>558.152</v>
       </c>
       <c r="F90">
-        <v>595.5840000000001</v>
+        <v>602.3520000000001</v>
       </c>
       <c r="G90">
         <v>85.09999999999999</v>
@@ -8893,37 +8893,37 @@
         <v>26.6</v>
       </c>
       <c r="M90">
-        <v>140.4387072</v>
+        <v>142.0346016</v>
       </c>
       <c r="N90">
-        <v>-113.8387072</v>
+        <v>-115.4346016</v>
       </c>
       <c r="O90">
-        <v>-14.2298384</v>
+        <v>-14.4293252</v>
       </c>
       <c r="P90">
-        <v>-99.60886880000001</v>
+        <v>-101.0052764</v>
       </c>
       <c r="Q90">
-        <v>-51.00886880000001</v>
+        <v>-52.40527640000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5220909554433281</v>
+        <v>0.5653901332109033</v>
       </c>
       <c r="T90">
-        <v>8.03094975865322</v>
+        <v>8.761036100348967</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02367580894393195</v>
+        <v>0.02340978861871923</v>
       </c>
       <c r="W90">
-        <v>0.2302172442510209</v>
+        <v>0.230279971843706</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1894064715514555</v>
+        <v>0.1872783089497537</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8939,22 +8939,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2671420895940977</v>
+        <v>0.2690420895940977</v>
       </c>
       <c r="C91">
-        <v>-360.2206296222954</v>
+        <v>-368.3251141725884</v>
       </c>
       <c r="D91">
-        <v>157.0313703777047</v>
+        <v>155.6948858274118</v>
       </c>
       <c r="E91">
-        <v>558.152</v>
+        <v>564.9200000000001</v>
       </c>
       <c r="F91">
-        <v>602.3520000000001</v>
+        <v>609.1200000000001</v>
       </c>
       <c r="G91">
         <v>85.09999999999999</v>
@@ -8975,37 +8975,37 @@
         <v>26.6</v>
       </c>
       <c r="M91">
-        <v>142.0346016</v>
+        <v>143.630496</v>
       </c>
       <c r="N91">
-        <v>-115.4346016</v>
+        <v>-117.030496</v>
       </c>
       <c r="O91">
-        <v>-14.4293252</v>
+        <v>-14.628812</v>
       </c>
       <c r="P91">
-        <v>-101.0052764</v>
+        <v>-102.401684</v>
       </c>
       <c r="Q91">
-        <v>-52.40527640000003</v>
+        <v>-53.80168400000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5653901332109033</v>
+        <v>0.6173491465319936</v>
       </c>
       <c r="T91">
-        <v>8.761036100348967</v>
+        <v>9.637139710383863</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02340978861871923</v>
+        <v>0.02314967985628901</v>
       </c>
       <c r="W91">
-        <v>0.230279971843706</v>
+        <v>0.2303413054898871</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1872783089497537</v>
+        <v>0.185197438850312</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2690420895940977</v>
+        <v>0.2709420895940977</v>
       </c>
       <c r="C92">
-        <v>-368.3251141725884</v>
+        <v>-376.407041229077</v>
       </c>
       <c r="D92">
-        <v>155.6948858274118</v>
+        <v>154.380958770923</v>
       </c>
       <c r="E92">
-        <v>564.9200000000001</v>
+        <v>571.688</v>
       </c>
       <c r="F92">
-        <v>609.1200000000001</v>
+        <v>615.888</v>
       </c>
       <c r="G92">
         <v>85.09999999999999</v>
@@ -9057,37 +9057,37 @@
         <v>26.6</v>
       </c>
       <c r="M92">
-        <v>143.630496</v>
+        <v>145.2263904</v>
       </c>
       <c r="N92">
-        <v>-117.030496</v>
+        <v>-118.6263904</v>
       </c>
       <c r="O92">
-        <v>-14.628812</v>
+        <v>-14.8282988</v>
       </c>
       <c r="P92">
-        <v>-102.401684</v>
+        <v>-103.7980916</v>
       </c>
       <c r="Q92">
-        <v>-53.80168400000002</v>
+        <v>-55.19809160000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6173491465319936</v>
+        <v>0.6808546072577708</v>
       </c>
       <c r="T92">
-        <v>9.637139710383863</v>
+        <v>10.70793301153763</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02314967985628901</v>
+        <v>0.02289528776995617</v>
       </c>
       <c r="W92">
-        <v>0.2303413054898871</v>
+        <v>0.2304012911438443</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.185197438850312</v>
+        <v>0.1831623021596493</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9103,22 +9103,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2709420895940977</v>
+        <v>0.2728420895940977</v>
       </c>
       <c r="C93">
-        <v>-376.407041229077</v>
+        <v>-384.4669771084074</v>
       </c>
       <c r="D93">
-        <v>154.380958770923</v>
+        <v>153.0890228915927</v>
       </c>
       <c r="E93">
-        <v>571.688</v>
+        <v>578.456</v>
       </c>
       <c r="F93">
-        <v>615.888</v>
+        <v>622.6560000000001</v>
       </c>
       <c r="G93">
         <v>85.09999999999999</v>
@@ -9139,37 +9139,37 @@
         <v>26.6</v>
       </c>
       <c r="M93">
-        <v>145.2263904</v>
+        <v>146.8222848</v>
       </c>
       <c r="N93">
-        <v>-118.6263904</v>
+        <v>-120.2222848</v>
       </c>
       <c r="O93">
-        <v>-14.8282988</v>
+        <v>-15.0277856</v>
       </c>
       <c r="P93">
-        <v>-103.7980916</v>
+        <v>-105.1944992</v>
       </c>
       <c r="Q93">
-        <v>-55.19809160000002</v>
+        <v>-56.59449920000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6808546072577708</v>
+        <v>0.7602364331649923</v>
       </c>
       <c r="T93">
-        <v>10.70793301153763</v>
+        <v>12.04642463797983</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02289528776995617</v>
+        <v>0.02264642594636969</v>
       </c>
       <c r="W93">
-        <v>0.2304012911438443</v>
+        <v>0.230459972761846</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1831623021596493</v>
+        <v>0.1811714075709574</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9185,22 +9185,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2728420895940977</v>
+        <v>0.2747420895940977</v>
       </c>
       <c r="C94">
-        <v>-384.4669771084074</v>
+        <v>-392.5054693276832</v>
       </c>
       <c r="D94">
-        <v>153.0890228915927</v>
+        <v>151.818530672317</v>
       </c>
       <c r="E94">
-        <v>578.456</v>
+        <v>585.224</v>
       </c>
       <c r="F94">
-        <v>622.6560000000001</v>
+        <v>629.4240000000001</v>
       </c>
       <c r="G94">
         <v>85.09999999999999</v>
@@ -9221,37 +9221,37 @@
         <v>26.6</v>
       </c>
       <c r="M94">
-        <v>146.8222848</v>
+        <v>148.4181792</v>
       </c>
       <c r="N94">
-        <v>-120.2222848</v>
+        <v>-121.8181792</v>
       </c>
       <c r="O94">
-        <v>-15.0277856</v>
+        <v>-15.2272724</v>
       </c>
       <c r="P94">
-        <v>-105.1944992</v>
+        <v>-106.5909068</v>
       </c>
       <c r="Q94">
-        <v>-56.59449920000004</v>
+        <v>-57.99090680000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7602364331649923</v>
+        <v>0.8622987807599913</v>
       </c>
       <c r="T94">
-        <v>12.04642463797983</v>
+        <v>13.76734244340553</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02264642594636969</v>
+        <v>0.02240291598995711</v>
       </c>
       <c r="W94">
-        <v>0.230459972761846</v>
+        <v>0.2305173924095681</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1811714075709574</v>
+        <v>0.1792233279196568</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9267,22 +9267,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2747420895940977</v>
+        <v>0.2766420895940978</v>
       </c>
       <c r="C95">
-        <v>-392.5054693276832</v>
+        <v>-400.5230473781357</v>
       </c>
       <c r="D95">
-        <v>151.818530672317</v>
+        <v>150.5689526218644</v>
       </c>
       <c r="E95">
-        <v>585.224</v>
+        <v>591.9920000000001</v>
       </c>
       <c r="F95">
-        <v>629.4240000000001</v>
+        <v>636.1920000000001</v>
       </c>
       <c r="G95">
         <v>85.09999999999999</v>
@@ -9303,37 +9303,37 @@
         <v>26.6</v>
       </c>
       <c r="M95">
-        <v>148.4181792</v>
+        <v>150.0140736</v>
       </c>
       <c r="N95">
-        <v>-121.8181792</v>
+        <v>-123.4140736000001</v>
       </c>
       <c r="O95">
-        <v>-15.2272724</v>
+        <v>-15.42675920000001</v>
       </c>
       <c r="P95">
-        <v>-106.5909068</v>
+        <v>-107.9873144</v>
       </c>
       <c r="Q95">
-        <v>-57.99090680000003</v>
+        <v>-59.38731440000004</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8622987807599913</v>
+        <v>0.998381910886657</v>
       </c>
       <c r="T95">
-        <v>13.76734244340553</v>
+        <v>16.06189951730645</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02240291598995711</v>
+        <v>0.02216458709644692</v>
       </c>
       <c r="W95">
-        <v>0.2305173924095681</v>
+        <v>0.2305735903626578</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1792233279196568</v>
+        <v>0.1773166967715754</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9349,22 +9349,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2766420895940978</v>
+        <v>0.2785420895940977</v>
       </c>
       <c r="C96">
-        <v>-400.5230473781357</v>
+        <v>-408.5202234608996</v>
       </c>
       <c r="D96">
-        <v>150.5689526218644</v>
+        <v>149.3397765391005</v>
       </c>
       <c r="E96">
-        <v>591.9920000000001</v>
+        <v>598.7600000000001</v>
       </c>
       <c r="F96">
-        <v>636.1920000000001</v>
+        <v>642.9600000000002</v>
       </c>
       <c r="G96">
         <v>85.09999999999999</v>
@@ -9385,37 +9385,37 @@
         <v>26.6</v>
       </c>
       <c r="M96">
-        <v>150.0140736</v>
+        <v>151.609968</v>
       </c>
       <c r="N96">
-        <v>-123.4140736000001</v>
+        <v>-125.009968</v>
       </c>
       <c r="O96">
-        <v>-15.42675920000001</v>
+        <v>-15.62624600000001</v>
       </c>
       <c r="P96">
-        <v>-107.9873144</v>
+        <v>-109.383722</v>
       </c>
       <c r="Q96">
-        <v>-59.38731440000004</v>
+        <v>-60.78372200000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.998381910886657</v>
+        <v>1.188898293063989</v>
       </c>
       <c r="T96">
-        <v>16.06189951730645</v>
+        <v>19.27427942076775</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02216458709644692</v>
+        <v>0.02193127565332643</v>
       </c>
       <c r="W96">
-        <v>0.2305735903626578</v>
+        <v>0.2306286052009456</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1773166967715754</v>
+        <v>0.1754502052266114</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9431,22 +9431,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2785420895940977</v>
+        <v>0.2804420895940977</v>
       </c>
       <c r="C97">
-        <v>-408.5202234608996</v>
+        <v>-416.4974931870393</v>
       </c>
       <c r="D97">
-        <v>149.3397765391005</v>
+        <v>148.1305068129608</v>
       </c>
       <c r="E97">
-        <v>598.7600000000001</v>
+        <v>605.528</v>
       </c>
       <c r="F97">
-        <v>642.9600000000002</v>
+        <v>649.7280000000001</v>
       </c>
       <c r="G97">
         <v>85.09999999999999</v>
@@ -9467,37 +9467,37 @@
         <v>26.6</v>
       </c>
       <c r="M97">
-        <v>151.609968</v>
+        <v>153.2058624</v>
       </c>
       <c r="N97">
-        <v>-125.009968</v>
+        <v>-126.6058624</v>
       </c>
       <c r="O97">
-        <v>-15.62624600000001</v>
+        <v>-15.8257328</v>
       </c>
       <c r="P97">
-        <v>-109.383722</v>
+        <v>-110.7801296</v>
       </c>
       <c r="Q97">
-        <v>-60.78372200000003</v>
+        <v>-62.18012960000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.188898293063989</v>
+        <v>1.474672866329986</v>
       </c>
       <c r="T97">
-        <v>19.27427942076775</v>
+        <v>24.0928492759597</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02193127565332643</v>
+        <v>0.02170282486527095</v>
       </c>
       <c r="W97">
-        <v>0.2306286052009456</v>
+        <v>0.2306824738967691</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1754502052266114</v>
+        <v>0.1736225989221676</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9513,22 +9513,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2804420895940977</v>
+        <v>0.2823420895940977</v>
       </c>
       <c r="C98">
-        <v>-416.4974931870393</v>
+        <v>-424.4553362438397</v>
       </c>
       <c r="D98">
-        <v>148.1305068129608</v>
+        <v>146.9406637561603</v>
       </c>
       <c r="E98">
-        <v>605.528</v>
+        <v>612.296</v>
       </c>
       <c r="F98">
-        <v>649.7280000000001</v>
+        <v>656.4960000000001</v>
       </c>
       <c r="G98">
         <v>85.09999999999999</v>
@@ -9549,37 +9549,37 @@
         <v>26.6</v>
       </c>
       <c r="M98">
-        <v>153.2058624</v>
+        <v>154.8017568</v>
       </c>
       <c r="N98">
-        <v>-126.6058624</v>
+        <v>-128.2017568</v>
       </c>
       <c r="O98">
-        <v>-15.8257328</v>
+        <v>-16.0252196</v>
       </c>
       <c r="P98">
-        <v>-110.7801296</v>
+        <v>-112.1765372</v>
       </c>
       <c r="Q98">
-        <v>-62.18012960000004</v>
+        <v>-63.57653720000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.474672866329983</v>
+        <v>1.950963821773311</v>
       </c>
       <c r="T98">
-        <v>24.09284927595963</v>
+        <v>32.12379903461285</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02170282486527095</v>
+        <v>0.02147908440274238</v>
       </c>
       <c r="W98">
-        <v>0.2306824738967691</v>
+        <v>0.2307352318978333</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1736225989221676</v>
+        <v>0.171832675221939</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9595,22 +9595,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2823420895940977</v>
+        <v>0.2842420895940977</v>
       </c>
       <c r="C99">
-        <v>-424.4553362438397</v>
+        <v>-432.3942170292412</v>
       </c>
       <c r="D99">
-        <v>146.9406637561603</v>
+        <v>145.7697829707589</v>
       </c>
       <c r="E99">
-        <v>612.296</v>
+        <v>619.064</v>
       </c>
       <c r="F99">
-        <v>656.4960000000001</v>
+        <v>663.264</v>
       </c>
       <c r="G99">
         <v>85.09999999999999</v>
@@ -9631,37 +9631,37 @@
         <v>26.6</v>
       </c>
       <c r="M99">
-        <v>154.8017568</v>
+        <v>156.3976512</v>
       </c>
       <c r="N99">
-        <v>-128.2017568</v>
+        <v>-129.7976512</v>
       </c>
       <c r="O99">
-        <v>-16.0252196</v>
+        <v>-16.2247064</v>
       </c>
       <c r="P99">
-        <v>-112.1765372</v>
+        <v>-113.5729448</v>
       </c>
       <c r="Q99">
-        <v>-63.57653720000003</v>
+        <v>-64.97294480000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.950963821773311</v>
+        <v>2.903545732659965</v>
       </c>
       <c r="T99">
-        <v>32.12379903461285</v>
+        <v>48.18569855191927</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02147908440274238</v>
+        <v>0.02125991007210216</v>
       </c>
       <c r="W99">
-        <v>0.2307352318978333</v>
+        <v>0.2307869132049983</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.171832675221939</v>
+        <v>0.1700792805768172</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9677,22 +9677,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2842420895940977</v>
+        <v>0.2861420895940977</v>
       </c>
       <c r="C100">
-        <v>-432.3942170292412</v>
+        <v>-440.3145852561805</v>
       </c>
       <c r="D100">
-        <v>145.7697829707589</v>
+        <v>144.6174147438195</v>
       </c>
       <c r="E100">
-        <v>619.064</v>
+        <v>625.832</v>
       </c>
       <c r="F100">
-        <v>663.264</v>
+        <v>670.032</v>
       </c>
       <c r="G100">
         <v>85.09999999999999</v>
@@ -9713,37 +9713,37 @@
         <v>26.6</v>
       </c>
       <c r="M100">
-        <v>156.3976512</v>
+        <v>157.9935456</v>
       </c>
       <c r="N100">
-        <v>-129.7976512</v>
+        <v>-131.3935456</v>
       </c>
       <c r="O100">
-        <v>-16.2247064</v>
+        <v>-16.4241932</v>
       </c>
       <c r="P100">
-        <v>-113.5729448</v>
+        <v>-114.9693524</v>
       </c>
       <c r="Q100">
-        <v>-64.97294480000002</v>
+        <v>-66.3693524</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.903545732659965</v>
+        <v>5.76129146531993</v>
       </c>
       <c r="T100">
-        <v>48.18569855191927</v>
+        <v>96.37139710383853</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02125991007210216</v>
+        <v>0.02104516350571729</v>
       </c>
       <c r="W100">
-        <v>0.2307869132049983</v>
+        <v>0.2308375504453519</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9751,91 +9751,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1700792805768172</v>
+        <v>0.1683613080457382</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2861420895940977</v>
-      </c>
-      <c r="C101">
-        <v>-440.3145852561805</v>
-      </c>
-      <c r="D101">
-        <v>144.6174147438195</v>
-      </c>
-      <c r="E101">
-        <v>625.832</v>
-      </c>
-      <c r="F101">
-        <v>670.032</v>
-      </c>
-      <c r="G101">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>632.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>75.2</v>
-      </c>
-      <c r="K101">
-        <v>48.6</v>
-      </c>
-      <c r="L101">
-        <v>26.6</v>
-      </c>
-      <c r="M101">
-        <v>157.9935456</v>
-      </c>
-      <c r="N101">
-        <v>-131.3935456</v>
-      </c>
-      <c r="O101">
-        <v>-16.4241932</v>
-      </c>
-      <c r="P101">
-        <v>-114.9693524</v>
-      </c>
-      <c r="Q101">
-        <v>-66.3693524</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.76129146531993</v>
-      </c>
-      <c r="T101">
-        <v>96.37139710383853</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02104516350571729</v>
-      </c>
-      <c r="W101">
-        <v>0.2308375504453519</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1683613080457382</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
